--- a/CARGAS_GENERAL.xlsx
+++ b/CARGAS_GENERAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aproy-Ludwig\15262-25 EDIFICIO ACADEMICO  U DE LIMA\PANASOLES\PARA_GIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ABF53F-EB3B-4F78-9634-2B58C215B595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641F47F6-6975-458B-BAA6-43CD829A3D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A55FB45B-D595-4128-A093-5BEC4E45278A}"/>
   </bookViews>
@@ -657,10 +657,10 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>-6.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F2">
-        <v>-2.2999999999999998</v>
+        <v>-1.9</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>10.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -689,10 +689,10 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>-17</v>
+        <v>-18.2</v>
       </c>
       <c r="F3">
-        <v>-2.2999999999999998</v>
+        <v>-1.9</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -721,10 +721,10 @@
         <v>13</v>
       </c>
       <c r="E4">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="F4">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="F5">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -785,22 +785,22 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>140.6</v>
+        <v>143.6</v>
       </c>
       <c r="F6">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="G6">
         <v>0.2</v>
       </c>
       <c r="H6">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J6">
-        <v>328.4</v>
+        <v>323.7</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -817,22 +817,22 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>140.6</v>
+        <v>143.6</v>
       </c>
       <c r="F7">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="G7">
         <v>0.2</v>
       </c>
       <c r="H7">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>154.6</v>
+        <v>152.80000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -849,22 +849,22 @@
         <v>13</v>
       </c>
       <c r="E8">
-        <v>-140.6</v>
+        <v>-143.6</v>
       </c>
       <c r="F8">
-        <v>-94.5</v>
+        <v>-93.5</v>
       </c>
       <c r="G8">
         <v>-0.2</v>
       </c>
       <c r="H8">
-        <v>-4.0999999999999996</v>
+        <v>-4.2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="J8">
-        <v>-328.4</v>
+        <v>-323.7</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -881,22 +881,22 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>-140.6</v>
+        <v>-143.6</v>
       </c>
       <c r="F9">
-        <v>-94.5</v>
+        <v>-93.5</v>
       </c>
       <c r="G9">
         <v>-0.2</v>
       </c>
       <c r="H9">
-        <v>-4.0999999999999996</v>
+        <v>-4.2</v>
       </c>
       <c r="I9">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="J9">
-        <v>-154.6</v>
+        <v>-152.80000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -913,22 +913,22 @@
         <v>13</v>
       </c>
       <c r="E10">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F10">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H10">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J10">
-        <v>163.80000000000001</v>
+        <v>167.8</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -945,22 +945,22 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F11">
-        <v>47.9</v>
+        <v>49</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H11">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I11">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11">
-        <v>86.2</v>
+        <v>85.9</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -977,22 +977,22 @@
         <v>13</v>
       </c>
       <c r="E12">
-        <v>-71.3</v>
+        <v>-69</v>
       </c>
       <c r="F12">
-        <v>-47.9</v>
+        <v>-49</v>
       </c>
       <c r="G12">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="H12">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="J12">
-        <v>-163.80000000000001</v>
+        <v>-167.8</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1009,22 +1009,22 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>-71.3</v>
+        <v>-69</v>
       </c>
       <c r="F13">
-        <v>-47.9</v>
+        <v>-49</v>
       </c>
       <c r="G13">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="H13">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="I13">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="J13">
-        <v>-86.2</v>
+        <v>-85.9</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1041,10 +1041,10 @@
         <v>13</v>
       </c>
       <c r="E14">
-        <v>-15.6</v>
+        <v>-16.3</v>
       </c>
       <c r="F14">
-        <v>-2.2999999999999998</v>
+        <v>-2.6</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1073,10 +1073,10 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>-22.7</v>
+        <v>-23.3</v>
       </c>
       <c r="F15">
-        <v>-2.2999999999999998</v>
+        <v>-2.6</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>-5</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1105,10 +1105,10 @@
         <v>13</v>
       </c>
       <c r="E16">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="F16">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1137,10 +1137,10 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="F17">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>13</v>
       </c>
       <c r="E18">
-        <v>252.4</v>
+        <v>249.9</v>
       </c>
       <c r="F18">
-        <v>355.6</v>
+        <v>357.4</v>
       </c>
       <c r="G18">
         <v>1.7</v>
@@ -1181,10 +1181,10 @@
         <v>0.8</v>
       </c>
       <c r="I18">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J18">
-        <v>344.7</v>
+        <v>349.9</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1201,10 +1201,10 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>252.4</v>
+        <v>249.9</v>
       </c>
       <c r="F19">
-        <v>355.6</v>
+        <v>357.4</v>
       </c>
       <c r="G19">
         <v>1.7</v>
@@ -1216,7 +1216,7 @@
         <v>3.5</v>
       </c>
       <c r="J19">
-        <v>904.3</v>
+        <v>906.1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1233,10 +1233,10 @@
         <v>13</v>
       </c>
       <c r="E20">
-        <v>-252.4</v>
+        <v>-249.9</v>
       </c>
       <c r="F20">
-        <v>-355.6</v>
+        <v>-357.4</v>
       </c>
       <c r="G20">
         <v>-1.7</v>
@@ -1245,10 +1245,10 @@
         <v>-0.8</v>
       </c>
       <c r="I20">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="J20">
-        <v>-344.7</v>
+        <v>-349.9</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1265,10 +1265,10 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>-252.4</v>
+        <v>-249.9</v>
       </c>
       <c r="F21">
-        <v>-355.6</v>
+        <v>-357.4</v>
       </c>
       <c r="G21">
         <v>-1.7</v>
@@ -1280,7 +1280,7 @@
         <v>-3.5</v>
       </c>
       <c r="J21">
-        <v>-904.3</v>
+        <v>-906.1</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1297,10 +1297,10 @@
         <v>13</v>
       </c>
       <c r="E22">
-        <v>145.19999999999999</v>
+        <v>148.9</v>
       </c>
       <c r="F22">
-        <v>141.30000000000001</v>
+        <v>140.69999999999999</v>
       </c>
       <c r="G22">
         <v>3.7</v>
@@ -1309,10 +1309,10 @@
         <v>0.5</v>
       </c>
       <c r="I22">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J22">
-        <v>167</v>
+        <v>165.4</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1329,10 +1329,10 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>145.19999999999999</v>
+        <v>148.9</v>
       </c>
       <c r="F23">
-        <v>141.30000000000001</v>
+        <v>140.69999999999999</v>
       </c>
       <c r="G23">
         <v>3.7</v>
@@ -1341,10 +1341,10 @@
         <v>0.5</v>
       </c>
       <c r="I23">
-        <v>8.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J23">
-        <v>368.5</v>
+        <v>367.9</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1361,10 +1361,10 @@
         <v>13</v>
       </c>
       <c r="E24">
-        <v>-145.19999999999999</v>
+        <v>-148.9</v>
       </c>
       <c r="F24">
-        <v>-141.30000000000001</v>
+        <v>-140.69999999999999</v>
       </c>
       <c r="G24">
         <v>-3.7</v>
@@ -1373,10 +1373,10 @@
         <v>-0.5</v>
       </c>
       <c r="I24">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="J24">
-        <v>-167</v>
+        <v>-165.4</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1393,10 +1393,10 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>-145.19999999999999</v>
+        <v>-148.9</v>
       </c>
       <c r="F25">
-        <v>-141.30000000000001</v>
+        <v>-140.69999999999999</v>
       </c>
       <c r="G25">
         <v>-3.7</v>
@@ -1405,10 +1405,10 @@
         <v>-0.5</v>
       </c>
       <c r="I25">
-        <v>-8.6</v>
+        <v>-8.6999999999999993</v>
       </c>
       <c r="J25">
-        <v>-368.5</v>
+        <v>-367.9</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1425,7 +1425,7 @@
         <v>13</v>
       </c>
       <c r="E26">
-        <v>-19</v>
+        <v>-18.899999999999999</v>
       </c>
       <c r="F26">
         <v>6.3</v>
@@ -1440,7 +1440,7 @@
         <v>-3.3</v>
       </c>
       <c r="J26">
-        <v>-17.399999999999999</v>
+        <v>-17.3</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1472,7 +1472,7 @@
         <v>2.1</v>
       </c>
       <c r="J27">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1504,7 +1504,7 @@
         <v>-0.7</v>
       </c>
       <c r="J28">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1536,7 +1536,7 @@
         <v>0.4</v>
       </c>
       <c r="J29">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1553,10 +1553,10 @@
         <v>13</v>
       </c>
       <c r="E30">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F30">
-        <v>127.1</v>
+        <v>127</v>
       </c>
       <c r="G30">
         <v>1.7</v>
@@ -1568,7 +1568,7 @@
         <v>2.7</v>
       </c>
       <c r="J30">
-        <v>546.70000000000005</v>
+        <v>546.9</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1585,10 +1585,10 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="F31">
-        <v>127.1</v>
+        <v>127</v>
       </c>
       <c r="G31">
         <v>1.7</v>
@@ -1600,7 +1600,7 @@
         <v>6.1</v>
       </c>
       <c r="J31">
-        <v>120.5</v>
+        <v>119.4</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1617,10 +1617,10 @@
         <v>13</v>
       </c>
       <c r="E32">
-        <v>-22.5</v>
+        <v>-22.7</v>
       </c>
       <c r="F32">
-        <v>-127.1</v>
+        <v>-127</v>
       </c>
       <c r="G32">
         <v>-1.7</v>
@@ -1632,7 +1632,7 @@
         <v>-2.7</v>
       </c>
       <c r="J32">
-        <v>-546.70000000000005</v>
+        <v>-546.9</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1649,10 +1649,10 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>-22.5</v>
+        <v>-22.7</v>
       </c>
       <c r="F33">
-        <v>-127.1</v>
+        <v>-127</v>
       </c>
       <c r="G33">
         <v>-1.7</v>
@@ -1664,7 +1664,7 @@
         <v>-6.1</v>
       </c>
       <c r="J33">
-        <v>-120.5</v>
+        <v>-119.4</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1684,7 +1684,7 @@
         <v>32.700000000000003</v>
       </c>
       <c r="F34">
-        <v>70.599999999999994</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="G34">
         <v>2.1</v>
@@ -1696,7 +1696,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="J34">
-        <v>270.8</v>
+        <v>270.3</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1716,7 +1716,7 @@
         <v>32.700000000000003</v>
       </c>
       <c r="F35">
-        <v>70.599999999999994</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="G35">
         <v>2.1</v>
@@ -1728,7 +1728,7 @@
         <v>5.6</v>
       </c>
       <c r="J35">
-        <v>97.6</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1748,7 +1748,7 @@
         <v>-32.700000000000003</v>
       </c>
       <c r="F36">
-        <v>-70.599999999999994</v>
+        <v>-70.400000000000006</v>
       </c>
       <c r="G36">
         <v>-2.1</v>
@@ -1760,7 +1760,7 @@
         <v>-5.0999999999999996</v>
       </c>
       <c r="J36">
-        <v>-270.8</v>
+        <v>-270.3</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1780,7 +1780,7 @@
         <v>-32.700000000000003</v>
       </c>
       <c r="F37">
-        <v>-70.599999999999994</v>
+        <v>-70.400000000000006</v>
       </c>
       <c r="G37">
         <v>-2.1</v>
@@ -1792,7 +1792,7 @@
         <v>-5.6</v>
       </c>
       <c r="J37">
-        <v>-97.6</v>
+        <v>-96.9</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1809,10 +1809,10 @@
         <v>13</v>
       </c>
       <c r="E38">
-        <v>-39.9</v>
+        <v>-39.799999999999997</v>
       </c>
       <c r="F38">
-        <v>-4.0999999999999996</v>
+        <v>-4</v>
       </c>
       <c r="G38">
         <v>0.4</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -1844,7 +1844,7 @@
         <v>-46.9</v>
       </c>
       <c r="F39">
-        <v>-4.0999999999999996</v>
+        <v>-4</v>
       </c>
       <c r="G39">
         <v>0.4</v>
@@ -1856,7 +1856,7 @@
         <v>0.5</v>
       </c>
       <c r="J39">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1888,7 +1888,7 @@
         <v>-0.2</v>
       </c>
       <c r="J40">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -1937,10 +1937,10 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="F42">
-        <v>200.8</v>
+        <v>200.4</v>
       </c>
       <c r="G42">
         <v>1.8</v>
@@ -1952,7 +1952,7 @@
         <v>3.1</v>
       </c>
       <c r="J42">
-        <v>114.6</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -1969,10 +1969,10 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="F43">
-        <v>200.8</v>
+        <v>200.4</v>
       </c>
       <c r="G43">
         <v>1.8</v>
@@ -1984,7 +1984,7 @@
         <v>3.5</v>
       </c>
       <c r="J43">
-        <v>728.5</v>
+        <v>728.1</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -2001,10 +2001,10 @@
         <v>13</v>
       </c>
       <c r="E44">
-        <v>-42.6</v>
+        <v>-42.8</v>
       </c>
       <c r="F44">
-        <v>-200.8</v>
+        <v>-200.4</v>
       </c>
       <c r="G44">
         <v>-1.8</v>
@@ -2016,7 +2016,7 @@
         <v>-3.1</v>
       </c>
       <c r="J44">
-        <v>-114.6</v>
+        <v>-113.3</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,10 +2033,10 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>-42.6</v>
+        <v>-42.8</v>
       </c>
       <c r="F45">
-        <v>-200.8</v>
+        <v>-200.4</v>
       </c>
       <c r="G45">
         <v>-1.8</v>
@@ -2048,7 +2048,7 @@
         <v>-3.5</v>
       </c>
       <c r="J45">
-        <v>-728.5</v>
+        <v>-728.1</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -2080,7 +2080,7 @@
         <v>3.5</v>
       </c>
       <c r="J46">
-        <v>108</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2112,7 +2112,7 @@
         <v>8.5</v>
       </c>
       <c r="J47">
-        <v>300.89999999999998</v>
+        <v>301</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -2144,7 +2144,7 @@
         <v>-3.5</v>
       </c>
       <c r="J48">
-        <v>-108</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2176,7 +2176,7 @@
         <v>-8.5</v>
       </c>
       <c r="J49">
-        <v>-300.89999999999998</v>
+        <v>-301</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2240,7 +2240,7 @@
         <v>-0.1</v>
       </c>
       <c r="J51">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="J54">
-        <v>520.9</v>
+        <v>521</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -2368,7 +2368,7 @@
         <v>3.8</v>
       </c>
       <c r="J55">
-        <v>113.7</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="J56">
-        <v>-520.9</v>
+        <v>-521</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -2432,7 +2432,7 @@
         <v>-3.8</v>
       </c>
       <c r="J57">
-        <v>-113.7</v>
+        <v>-112.7</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="F58">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="G58">
         <v>1.3</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="J58">
-        <v>291.3</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="F59">
-        <v>77</v>
+        <v>76.8</v>
       </c>
       <c r="G59">
         <v>1.3</v>
@@ -2496,7 +2496,7 @@
         <v>6.3</v>
       </c>
       <c r="J59">
-        <v>108.1</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2516,7 +2516,7 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="F60">
-        <v>-77</v>
+        <v>-76.8</v>
       </c>
       <c r="G60">
         <v>-1.3</v>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>-291.3</v>
+        <v>-290.7</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="F61">
-        <v>-77</v>
+        <v>-76.8</v>
       </c>
       <c r="G61">
         <v>-1.3</v>
@@ -2560,7 +2560,7 @@
         <v>-6.3</v>
       </c>
       <c r="J61">
-        <v>-108.1</v>
+        <v>-107.7</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2592,7 +2592,7 @@
         <v>-0.1</v>
       </c>
       <c r="J62">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -2708,7 +2708,7 @@
         <v>6.9</v>
       </c>
       <c r="F66">
-        <v>196.6</v>
+        <v>196.3</v>
       </c>
       <c r="G66">
         <v>1.3</v>
@@ -2720,7 +2720,7 @@
         <v>3.8</v>
       </c>
       <c r="J66">
-        <v>113.7</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -2740,7 +2740,7 @@
         <v>6.9</v>
       </c>
       <c r="F67">
-        <v>196.6</v>
+        <v>196.3</v>
       </c>
       <c r="G67">
         <v>1.3</v>
@@ -2752,7 +2752,7 @@
         <v>1.8</v>
       </c>
       <c r="J67">
-        <v>723.9</v>
+        <v>723.6</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2772,7 +2772,7 @@
         <v>-6.9</v>
       </c>
       <c r="F68">
-        <v>-196.6</v>
+        <v>-196.3</v>
       </c>
       <c r="G68">
         <v>-1.3</v>
@@ -2784,7 +2784,7 @@
         <v>-3.8</v>
       </c>
       <c r="J68">
-        <v>-113.7</v>
+        <v>-112.7</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -2804,7 +2804,7 @@
         <v>-6.9</v>
       </c>
       <c r="F69">
-        <v>-196.6</v>
+        <v>-196.3</v>
       </c>
       <c r="G69">
         <v>-1.3</v>
@@ -2816,7 +2816,7 @@
         <v>-1.8</v>
       </c>
       <c r="J69">
-        <v>-723.9</v>
+        <v>-723.6</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -2836,7 +2836,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="F70">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="G70">
         <v>1.8</v>
@@ -2848,7 +2848,7 @@
         <v>6.3</v>
       </c>
       <c r="J70">
-        <v>108.1</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -2868,7 +2868,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="F71">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="G71">
         <v>1.8</v>
@@ -2880,7 +2880,7 @@
         <v>5.4</v>
       </c>
       <c r="J71">
-        <v>297.89999999999998</v>
+        <v>298.10000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -2900,7 +2900,7 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="F72">
-        <v>-78.7</v>
+        <v>-78.8</v>
       </c>
       <c r="G72">
         <v>-1.8</v>
@@ -2912,7 +2912,7 @@
         <v>-6.3</v>
       </c>
       <c r="J72">
-        <v>-108.1</v>
+        <v>-107.7</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -2932,7 +2932,7 @@
         <v>-20.100000000000001</v>
       </c>
       <c r="F73">
-        <v>-78.7</v>
+        <v>-78.8</v>
       </c>
       <c r="G73">
         <v>-1.8</v>
@@ -2944,7 +2944,7 @@
         <v>-5.4</v>
       </c>
       <c r="J73">
-        <v>-297.89999999999998</v>
+        <v>-298.10000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
@@ -2976,7 +2976,7 @@
         <v>-5.3</v>
       </c>
       <c r="J74">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
@@ -3008,7 +3008,7 @@
         <v>3.1</v>
       </c>
       <c r="J75">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -3136,7 +3136,7 @@
         <v>9.1</v>
       </c>
       <c r="J79">
-        <v>116</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -3200,7 +3200,7 @@
         <v>-9.1</v>
       </c>
       <c r="J81">
-        <v>-116</v>
+        <v>-115.4</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -3220,19 +3220,19 @@
         <v>49.1</v>
       </c>
       <c r="F82">
-        <v>68.099999999999994</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G82">
         <v>9.3000000000000007</v>
       </c>
       <c r="H82">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I82">
         <v>21.6</v>
       </c>
       <c r="J82">
-        <v>261.3</v>
+        <v>260.89999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -3252,19 +3252,19 @@
         <v>49.1</v>
       </c>
       <c r="F83">
-        <v>68.099999999999994</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="G83">
         <v>9.3000000000000007</v>
       </c>
       <c r="H83">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I83">
         <v>24.6</v>
       </c>
       <c r="J83">
-        <v>90.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -3284,19 +3284,19 @@
         <v>-49.1</v>
       </c>
       <c r="F84">
-        <v>-68.099999999999994</v>
+        <v>-67.900000000000006</v>
       </c>
       <c r="G84">
         <v>-9.3000000000000007</v>
       </c>
       <c r="H84">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="I84">
         <v>-21.6</v>
       </c>
       <c r="J84">
-        <v>-261.3</v>
+        <v>-260.89999999999998</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -3316,19 +3316,19 @@
         <v>-49.1</v>
       </c>
       <c r="F85">
-        <v>-68.099999999999994</v>
+        <v>-67.900000000000006</v>
       </c>
       <c r="G85">
         <v>-9.3000000000000007</v>
       </c>
       <c r="H85">
-        <v>-5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="I85">
         <v>-24.6</v>
       </c>
       <c r="J85">
-        <v>-90.7</v>
+        <v>-90.2</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -3360,7 +3360,7 @@
         <v>-1.4</v>
       </c>
       <c r="J86">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -3476,7 +3476,7 @@
         <v>42.5</v>
       </c>
       <c r="F90">
-        <v>191.4</v>
+        <v>191.2</v>
       </c>
       <c r="G90">
         <v>1.2</v>
@@ -3488,7 +3488,7 @@
         <v>2.9</v>
       </c>
       <c r="J90">
-        <v>116</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -3508,7 +3508,7 @@
         <v>42.5</v>
       </c>
       <c r="F91">
-        <v>191.4</v>
+        <v>191.2</v>
       </c>
       <c r="G91">
         <v>1.2</v>
@@ -3520,7 +3520,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="J91">
-        <v>717.9</v>
+        <v>717.7</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3540,7 +3540,7 @@
         <v>-42.5</v>
       </c>
       <c r="F92">
-        <v>-191.4</v>
+        <v>-191.2</v>
       </c>
       <c r="G92">
         <v>-1.2</v>
@@ -3552,7 +3552,7 @@
         <v>-2.9</v>
       </c>
       <c r="J92">
-        <v>-116</v>
+        <v>-115.4</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -3572,7 +3572,7 @@
         <v>-42.5</v>
       </c>
       <c r="F93">
-        <v>-191.4</v>
+        <v>-191.2</v>
       </c>
       <c r="G93">
         <v>-1.2</v>
@@ -3584,7 +3584,7 @@
         <v>-2.2999999999999998</v>
       </c>
       <c r="J93">
-        <v>-717.9</v>
+        <v>-717.7</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3604,7 +3604,7 @@
         <v>90.1</v>
       </c>
       <c r="F94">
-        <v>76.400000000000006</v>
+        <v>76.5</v>
       </c>
       <c r="G94">
         <v>2.7</v>
@@ -3616,7 +3616,7 @@
         <v>6.2</v>
       </c>
       <c r="J94">
-        <v>90.7</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -3636,7 +3636,7 @@
         <v>90.1</v>
       </c>
       <c r="F95">
-        <v>76.400000000000006</v>
+        <v>76.5</v>
       </c>
       <c r="G95">
         <v>2.7</v>
@@ -3648,7 +3648,7 @@
         <v>7.3</v>
       </c>
       <c r="J95">
-        <v>298.7</v>
+        <v>298.89999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -3668,7 +3668,7 @@
         <v>-90.1</v>
       </c>
       <c r="F96">
-        <v>-76.400000000000006</v>
+        <v>-76.5</v>
       </c>
       <c r="G96">
         <v>-2.7</v>
@@ -3680,7 +3680,7 @@
         <v>-6.2</v>
       </c>
       <c r="J96">
-        <v>-90.7</v>
+        <v>-90.2</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -3700,7 +3700,7 @@
         <v>-90.1</v>
       </c>
       <c r="F97">
-        <v>-76.400000000000006</v>
+        <v>-76.5</v>
       </c>
       <c r="G97">
         <v>-2.7</v>
@@ -3712,7 +3712,7 @@
         <v>-7.3</v>
       </c>
       <c r="J97">
-        <v>-298.7</v>
+        <v>-298.89999999999998</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -3776,7 +3776,7 @@
         <v>-0.2</v>
       </c>
       <c r="J99">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="J102">
-        <v>496.7</v>
+        <v>496.8</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -3904,7 +3904,7 @@
         <v>4.8</v>
       </c>
       <c r="J103">
-        <v>106</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>-496.7</v>
+        <v>-496.8</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -3968,7 +3968,7 @@
         <v>-4.8</v>
       </c>
       <c r="J105">
-        <v>-106</v>
+        <v>-105.6</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -3988,7 +3988,7 @@
         <v>21.7</v>
       </c>
       <c r="F106">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="G106">
         <v>2.8</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="J106">
-        <v>232.5</v>
+        <v>232.2</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -4020,7 +4020,7 @@
         <v>21.7</v>
       </c>
       <c r="F107">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="G107">
         <v>2.8</v>
@@ -4032,7 +4032,7 @@
         <v>13.8</v>
       </c>
       <c r="J107">
-        <v>62</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -4052,7 +4052,7 @@
         <v>-21.7</v>
       </c>
       <c r="F108">
-        <v>-56.1</v>
+        <v>-55.9</v>
       </c>
       <c r="G108">
         <v>-2.8</v>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>-232.5</v>
+        <v>-232.2</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -4084,7 +4084,7 @@
         <v>-21.7</v>
       </c>
       <c r="F109">
-        <v>-56.1</v>
+        <v>-55.9</v>
       </c>
       <c r="G109">
         <v>-2.8</v>
@@ -4096,7 +4096,7 @@
         <v>-13.8</v>
       </c>
       <c r="J109">
-        <v>-62</v>
+        <v>-61.6</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -4116,7 +4116,7 @@
         <v>-26.9</v>
       </c>
       <c r="F110">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="G110">
         <v>0.1</v>
@@ -4128,7 +4128,7 @@
         <v>-0.2</v>
       </c>
       <c r="J110">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -4148,7 +4148,7 @@
         <v>-34</v>
       </c>
       <c r="F111">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="G111">
         <v>0.1</v>
@@ -4160,7 +4160,7 @@
         <v>0.1</v>
       </c>
       <c r="J111">
-        <v>-5.6</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -4244,7 +4244,7 @@
         <v>9.9</v>
       </c>
       <c r="F114">
-        <v>196.8</v>
+        <v>196.7</v>
       </c>
       <c r="G114">
         <v>1.5</v>
@@ -4256,7 +4256,7 @@
         <v>4.8</v>
       </c>
       <c r="J114">
-        <v>106</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
@@ -4276,7 +4276,7 @@
         <v>9.9</v>
       </c>
       <c r="F115">
-        <v>196.8</v>
+        <v>196.7</v>
       </c>
       <c r="G115">
         <v>1.5</v>
@@ -4288,7 +4288,7 @@
         <v>1.7</v>
       </c>
       <c r="J115">
-        <v>724.8</v>
+        <v>724.6</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
@@ -4308,7 +4308,7 @@
         <v>-9.9</v>
       </c>
       <c r="F116">
-        <v>-196.8</v>
+        <v>-196.7</v>
       </c>
       <c r="G116">
         <v>-1.5</v>
@@ -4320,7 +4320,7 @@
         <v>-4.8</v>
       </c>
       <c r="J116">
-        <v>-106</v>
+        <v>-105.6</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -4340,7 +4340,7 @@
         <v>-9.9</v>
       </c>
       <c r="F117">
-        <v>-196.8</v>
+        <v>-196.7</v>
       </c>
       <c r="G117">
         <v>-1.5</v>
@@ -4352,7 +4352,7 @@
         <v>-1.7</v>
       </c>
       <c r="J117">
-        <v>-724.8</v>
+        <v>-724.6</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -4384,7 +4384,7 @@
         <v>13.8</v>
       </c>
       <c r="J118">
-        <v>62</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -4416,7 +4416,7 @@
         <v>4.7</v>
       </c>
       <c r="J119">
-        <v>308.60000000000002</v>
+        <v>308.7</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -4448,7 +4448,7 @@
         <v>-13.8</v>
       </c>
       <c r="J120">
-        <v>-62</v>
+        <v>-61.6</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -4480,7 +4480,7 @@
         <v>-4.7</v>
       </c>
       <c r="J121">
-        <v>-308.60000000000002</v>
+        <v>-308.7</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -4512,7 +4512,7 @@
         <v>-4.7</v>
       </c>
       <c r="J122">
-        <v>-1.1000000000000001</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -4640,7 +4640,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="J126">
-        <v>481.8</v>
+        <v>481.7</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -4672,7 +4672,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="J127">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -4704,7 +4704,7 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="J128">
-        <v>-481.8</v>
+        <v>-481.7</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -4736,7 +4736,7 @@
         <v>-9.8000000000000007</v>
       </c>
       <c r="J129">
-        <v>-106.5</v>
+        <v>-106.1</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -4756,7 +4756,7 @@
         <v>71.599999999999994</v>
       </c>
       <c r="F130">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="G130">
         <v>11.4</v>
@@ -4768,7 +4768,7 @@
         <v>26.1</v>
       </c>
       <c r="J130">
-        <v>207.9</v>
+        <v>207.6</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -4788,7 +4788,7 @@
         <v>71.599999999999994</v>
       </c>
       <c r="F131">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="G131">
         <v>11.4</v>
@@ -4800,7 +4800,7 @@
         <v>30.8</v>
       </c>
       <c r="J131">
-        <v>64.400000000000006</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>-71.599999999999994</v>
       </c>
       <c r="F132">
-        <v>-48.4</v>
+        <v>-48.2</v>
       </c>
       <c r="G132">
         <v>-11.4</v>
@@ -4832,7 +4832,7 @@
         <v>-26.1</v>
       </c>
       <c r="J132">
-        <v>-207.9</v>
+        <v>-207.6</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -4852,7 +4852,7 @@
         <v>-71.599999999999994</v>
       </c>
       <c r="F133">
-        <v>-48.4</v>
+        <v>-48.2</v>
       </c>
       <c r="G133">
         <v>-11.4</v>
@@ -4864,7 +4864,7 @@
         <v>-30.8</v>
       </c>
       <c r="J133">
-        <v>-64.400000000000006</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -4884,7 +4884,7 @@
         <v>-44</v>
       </c>
       <c r="F134">
-        <v>-2.2999999999999998</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="G134">
         <v>0.6</v>
@@ -4916,7 +4916,7 @@
         <v>-51</v>
       </c>
       <c r="F135">
-        <v>-2.2999999999999998</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="G135">
         <v>0.6</v>
@@ -5012,7 +5012,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="F138">
-        <v>200.8</v>
+        <v>200.7</v>
       </c>
       <c r="G138">
         <v>1.2</v>
@@ -5024,7 +5024,7 @@
         <v>3.2</v>
       </c>
       <c r="J138">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -5044,7 +5044,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="F139">
-        <v>200.8</v>
+        <v>200.7</v>
       </c>
       <c r="G139">
         <v>1.2</v>
@@ -5056,7 +5056,7 @@
         <v>2.6</v>
       </c>
       <c r="J139">
-        <v>729.5</v>
+        <v>729.3</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -5076,7 +5076,7 @@
         <v>-37.299999999999997</v>
       </c>
       <c r="F140">
-        <v>-200.8</v>
+        <v>-200.7</v>
       </c>
       <c r="G140">
         <v>-1.2</v>
@@ -5088,7 +5088,7 @@
         <v>-3.2</v>
       </c>
       <c r="J140">
-        <v>-106.5</v>
+        <v>-106.1</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -5108,7 +5108,7 @@
         <v>-37.299999999999997</v>
       </c>
       <c r="F141">
-        <v>-200.8</v>
+        <v>-200.7</v>
       </c>
       <c r="G141">
         <v>-1.2</v>
@@ -5120,7 +5120,7 @@
         <v>-2.6</v>
       </c>
       <c r="J141">
-        <v>-729.5</v>
+        <v>-729.3</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -5152,7 +5152,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="J142">
-        <v>64.400000000000006</v>
+        <v>64</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -5184,7 +5184,7 @@
         <v>7.7</v>
       </c>
       <c r="J143">
-        <v>319.3</v>
+        <v>319.39999999999998</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -5216,7 +5216,7 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="J144">
-        <v>-64.400000000000006</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -5248,7 +5248,7 @@
         <v>-7.7</v>
       </c>
       <c r="J145">
-        <v>-319.3</v>
+        <v>-319.39999999999998</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -5396,7 +5396,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F150">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="G150">
         <v>0.9</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <v>475.6</v>
+        <v>475.5</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -5428,7 +5428,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F151">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="G151">
         <v>0.9</v>
@@ -5440,7 +5440,7 @@
         <v>4.5</v>
       </c>
       <c r="J151">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -5460,7 +5460,7 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="F152">
-        <v>-107</v>
+        <v>-106.9</v>
       </c>
       <c r="G152">
         <v>-0.9</v>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <v>-475.6</v>
+        <v>-475.5</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -5492,7 +5492,7 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="F153">
-        <v>-107</v>
+        <v>-106.9</v>
       </c>
       <c r="G153">
         <v>-0.9</v>
@@ -5504,7 +5504,7 @@
         <v>-4.5</v>
       </c>
       <c r="J153">
-        <v>-104.2</v>
+        <v>-103.8</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -5524,7 +5524,7 @@
         <v>28.3</v>
       </c>
       <c r="F154">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="G154">
         <v>2.8</v>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <v>201.3</v>
+        <v>201.1</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -5556,7 +5556,7 @@
         <v>28.3</v>
       </c>
       <c r="F155">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="G155">
         <v>2.8</v>
@@ -5568,7 +5568,7 @@
         <v>14.1</v>
       </c>
       <c r="J155">
-        <v>73.900000000000006</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -5588,7 +5588,7 @@
         <v>-28.3</v>
       </c>
       <c r="F156">
-        <v>-47.9</v>
+        <v>-47.7</v>
       </c>
       <c r="G156">
         <v>-2.8</v>
@@ -5600,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="J156">
-        <v>-201.3</v>
+        <v>-201.1</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -5620,7 +5620,7 @@
         <v>-28.3</v>
       </c>
       <c r="F157">
-        <v>-47.9</v>
+        <v>-47.7</v>
       </c>
       <c r="G157">
         <v>-2.8</v>
@@ -5632,7 +5632,7 @@
         <v>-14.1</v>
       </c>
       <c r="J157">
-        <v>-73.900000000000006</v>
+        <v>-73.5</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -5696,7 +5696,7 @@
         <v>0.2</v>
       </c>
       <c r="J159">
-        <v>-5.2</v>
+        <v>-5.0999999999999996</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -5780,7 +5780,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F162">
-        <v>204</v>
+        <v>203.9</v>
       </c>
       <c r="G162">
         <v>1.4</v>
@@ -5792,7 +5792,7 @@
         <v>4.5</v>
       </c>
       <c r="J162">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -5812,7 +5812,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F163">
-        <v>204</v>
+        <v>203.9</v>
       </c>
       <c r="G163">
         <v>1.4</v>
@@ -5824,7 +5824,7 @@
         <v>1.9</v>
       </c>
       <c r="J163">
-        <v>733.3</v>
+        <v>733.2</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -5844,7 +5844,7 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="F164">
-        <v>-204</v>
+        <v>-203.9</v>
       </c>
       <c r="G164">
         <v>-1.4</v>
@@ -5856,7 +5856,7 @@
         <v>-4.5</v>
       </c>
       <c r="J164">
-        <v>-104.2</v>
+        <v>-103.8</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -5876,7 +5876,7 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="F165">
-        <v>-204</v>
+        <v>-203.9</v>
       </c>
       <c r="G165">
         <v>-1.4</v>
@@ -5888,7 +5888,7 @@
         <v>-1.9</v>
       </c>
       <c r="J165">
-        <v>-733.3</v>
+        <v>-733.2</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -5920,7 +5920,7 @@
         <v>14.1</v>
       </c>
       <c r="J166">
-        <v>73.900000000000006</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -5952,7 +5952,7 @@
         <v>5.3</v>
       </c>
       <c r="J167">
-        <v>323.8</v>
+        <v>323.89999999999998</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -5984,7 +5984,7 @@
         <v>-14.1</v>
       </c>
       <c r="J168">
-        <v>-73.900000000000006</v>
+        <v>-73.5</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -6016,7 +6016,7 @@
         <v>-5.3</v>
       </c>
       <c r="J169">
-        <v>-323.8</v>
+        <v>-323.89999999999998</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -6080,7 +6080,7 @@
         <v>2.9</v>
       </c>
       <c r="J171">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -6176,7 +6176,7 @@
         <v>8</v>
       </c>
       <c r="J174">
-        <v>471.5</v>
+        <v>471.4</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -6208,7 +6208,7 @@
         <v>8.9</v>
       </c>
       <c r="J175">
-        <v>107.4</v>
+        <v>107</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -6240,7 +6240,7 @@
         <v>-8</v>
       </c>
       <c r="J176">
-        <v>-471.5</v>
+        <v>-471.4</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -6272,7 +6272,7 @@
         <v>-8.9</v>
       </c>
       <c r="J177">
-        <v>-107.4</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -6292,7 +6292,7 @@
         <v>46.9</v>
       </c>
       <c r="F178">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G178">
         <v>11.4</v>
@@ -6304,7 +6304,7 @@
         <v>27</v>
       </c>
       <c r="J178">
-        <v>203</v>
+        <v>202.8</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -6324,7 +6324,7 @@
         <v>46.9</v>
       </c>
       <c r="F179">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="G179">
         <v>11.4</v>
@@ -6336,7 +6336,7 @@
         <v>29.9</v>
       </c>
       <c r="J179">
-        <v>78.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -6356,7 +6356,7 @@
         <v>-46.9</v>
       </c>
       <c r="F180">
-        <v>-48.7</v>
+        <v>-48.5</v>
       </c>
       <c r="G180">
         <v>-11.4</v>
@@ -6368,7 +6368,7 @@
         <v>-27</v>
       </c>
       <c r="J180">
-        <v>-203</v>
+        <v>-202.8</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -6388,7 +6388,7 @@
         <v>-46.9</v>
       </c>
       <c r="F181">
-        <v>-48.7</v>
+        <v>-48.5</v>
       </c>
       <c r="G181">
         <v>-11.4</v>
@@ -6400,7 +6400,7 @@
         <v>-29.9</v>
       </c>
       <c r="J181">
-        <v>-78.5</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -6432,7 +6432,7 @@
         <v>-1.5</v>
       </c>
       <c r="J182">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -6484,7 +6484,7 @@
         <v>-5.5</v>
       </c>
       <c r="F184">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -6516,7 +6516,7 @@
         <v>-5.5</v>
       </c>
       <c r="F185">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G185">
         <v>0.1</v>
@@ -6548,7 +6548,7 @@
         <v>25.4</v>
       </c>
       <c r="F186">
-        <v>205.2</v>
+        <v>205.1</v>
       </c>
       <c r="G186">
         <v>1.2</v>
@@ -6560,7 +6560,7 @@
         <v>2.9</v>
       </c>
       <c r="J186">
-        <v>107.4</v>
+        <v>107</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -6580,7 +6580,7 @@
         <v>25.4</v>
       </c>
       <c r="F187">
-        <v>205.2</v>
+        <v>205.1</v>
       </c>
       <c r="G187">
         <v>1.2</v>
@@ -6592,7 +6592,7 @@
         <v>3</v>
       </c>
       <c r="J187">
-        <v>734.6</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -6612,7 +6612,7 @@
         <v>-25.4</v>
       </c>
       <c r="F188">
-        <v>-205.2</v>
+        <v>-205.1</v>
       </c>
       <c r="G188">
         <v>-1.2</v>
@@ -6624,7 +6624,7 @@
         <v>-2.9</v>
       </c>
       <c r="J188">
-        <v>-107.4</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -6644,7 +6644,7 @@
         <v>-25.4</v>
       </c>
       <c r="F189">
-        <v>-205.2</v>
+        <v>-205.1</v>
       </c>
       <c r="G189">
         <v>-1.2</v>
@@ -6656,7 +6656,7 @@
         <v>-3</v>
       </c>
       <c r="J189">
-        <v>-734.6</v>
+        <v>-734.5</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -6676,7 +6676,7 @@
         <v>87.5</v>
       </c>
       <c r="F190">
-        <v>95.6</v>
+        <v>95.5</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -6688,7 +6688,7 @@
         <v>8.4</v>
       </c>
       <c r="J190">
-        <v>78.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -6708,7 +6708,7 @@
         <v>87.5</v>
       </c>
       <c r="F191">
-        <v>95.6</v>
+        <v>95.5</v>
       </c>
       <c r="G191">
         <v>3</v>
@@ -6740,7 +6740,7 @@
         <v>-87.5</v>
       </c>
       <c r="F192">
-        <v>-95.6</v>
+        <v>-95.5</v>
       </c>
       <c r="G192">
         <v>-3</v>
@@ -6752,7 +6752,7 @@
         <v>-8.4</v>
       </c>
       <c r="J192">
-        <v>-78.5</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -6772,7 +6772,7 @@
         <v>-87.5</v>
       </c>
       <c r="F193">
-        <v>-95.6</v>
+        <v>-95.5</v>
       </c>
       <c r="G193">
         <v>-3</v>
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="J198">
-        <v>471.3</v>
+        <v>471.2</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -6976,7 +6976,7 @@
         <v>3.8</v>
       </c>
       <c r="J199">
-        <v>105.3</v>
+        <v>105</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -7008,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>-471.3</v>
+        <v>-471.2</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -7040,7 +7040,7 @@
         <v>-3.8</v>
       </c>
       <c r="J201">
-        <v>-105.3</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -7060,7 +7060,7 @@
         <v>32.1</v>
       </c>
       <c r="F202">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="G202">
         <v>2.5</v>
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="J202">
-        <v>211.3</v>
+        <v>211.1</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -7092,7 +7092,7 @@
         <v>32.1</v>
       </c>
       <c r="F203">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="G203">
         <v>2.5</v>
@@ -7104,7 +7104,7 @@
         <v>12.7</v>
       </c>
       <c r="J203">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -7124,7 +7124,7 @@
         <v>-32.1</v>
       </c>
       <c r="F204">
-        <v>-50.2</v>
+        <v>-50.1</v>
       </c>
       <c r="G204">
         <v>-2.5</v>
@@ -7136,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="J204">
-        <v>-211.3</v>
+        <v>-211.1</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>-32.1</v>
       </c>
       <c r="F205">
-        <v>-50.2</v>
+        <v>-50.1</v>
       </c>
       <c r="G205">
         <v>-2.5</v>
@@ -7168,7 +7168,7 @@
         <v>-12.7</v>
       </c>
       <c r="J205">
-        <v>-74.7</v>
+        <v>-74.3</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -7316,7 +7316,7 @@
         <v>9.5</v>
       </c>
       <c r="F210">
-        <v>206</v>
+        <v>205.9</v>
       </c>
       <c r="G210">
         <v>1.1000000000000001</v>
@@ -7328,7 +7328,7 @@
         <v>3.8</v>
       </c>
       <c r="J210">
-        <v>105.3</v>
+        <v>105</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -7348,7 +7348,7 @@
         <v>9.5</v>
       </c>
       <c r="F211">
-        <v>206</v>
+        <v>205.9</v>
       </c>
       <c r="G211">
         <v>1.1000000000000001</v>
@@ -7360,7 +7360,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J211">
-        <v>735.7</v>
+        <v>735.5</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -7380,7 +7380,7 @@
         <v>-9.5</v>
       </c>
       <c r="F212">
-        <v>-206</v>
+        <v>-205.9</v>
       </c>
       <c r="G212">
         <v>-1.1000000000000001</v>
@@ -7392,7 +7392,7 @@
         <v>-3.8</v>
       </c>
       <c r="J212">
-        <v>-105.3</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -7412,7 +7412,7 @@
         <v>-9.5</v>
       </c>
       <c r="F213">
-        <v>-206</v>
+        <v>-205.9</v>
       </c>
       <c r="G213">
         <v>-1.1000000000000001</v>
@@ -7424,7 +7424,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="J213">
-        <v>-735.7</v>
+        <v>-735.5</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -7456,7 +7456,7 @@
         <v>12.7</v>
       </c>
       <c r="J214">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <v>-12.7</v>
       </c>
       <c r="J216">
-        <v>-74.7</v>
+        <v>-74.3</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>23.3</v>
       </c>
       <c r="F222">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="G222">
         <v>3.3</v>
@@ -7712,7 +7712,7 @@
         <v>7.6</v>
       </c>
       <c r="J222">
-        <v>471.8</v>
+        <v>471.7</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -7732,7 +7732,7 @@
         <v>23.3</v>
       </c>
       <c r="F223">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="G223">
         <v>3.3</v>
@@ -7744,7 +7744,7 @@
         <v>9</v>
       </c>
       <c r="J223">
-        <v>108.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -7764,7 +7764,7 @@
         <v>-23.3</v>
       </c>
       <c r="F224">
-        <v>-106.3</v>
+        <v>-106.2</v>
       </c>
       <c r="G224">
         <v>-3.3</v>
@@ -7776,7 +7776,7 @@
         <v>-7.6</v>
       </c>
       <c r="J224">
-        <v>-471.8</v>
+        <v>-471.7</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -7796,7 +7796,7 @@
         <v>-23.3</v>
       </c>
       <c r="F225">
-        <v>-106.3</v>
+        <v>-106.2</v>
       </c>
       <c r="G225">
         <v>-3.3</v>
@@ -7808,7 +7808,7 @@
         <v>-9</v>
       </c>
       <c r="J225">
-        <v>-108.3</v>
+        <v>-107.9</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -7828,7 +7828,7 @@
         <v>77.900000000000006</v>
       </c>
       <c r="F226">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="G226">
         <v>11.1</v>
@@ -7840,7 +7840,7 @@
         <v>25.4</v>
       </c>
       <c r="J226">
-        <v>209.1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -7860,7 +7860,7 @@
         <v>77.900000000000006</v>
       </c>
       <c r="F227">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="G227">
         <v>11.1</v>
@@ -7872,7 +7872,7 @@
         <v>30</v>
       </c>
       <c r="J227">
-        <v>78.3</v>
+        <v>78.099999999999994</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -7892,7 +7892,7 @@
         <v>-77.900000000000006</v>
       </c>
       <c r="F228">
-        <v>-50.8</v>
+        <v>-50.7</v>
       </c>
       <c r="G228">
         <v>-11.1</v>
@@ -7904,7 +7904,7 @@
         <v>-25.4</v>
       </c>
       <c r="J228">
-        <v>-209.1</v>
+        <v>-209</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -7924,7 +7924,7 @@
         <v>-77.900000000000006</v>
       </c>
       <c r="F229">
-        <v>-50.8</v>
+        <v>-50.7</v>
       </c>
       <c r="G229">
         <v>-11.1</v>
@@ -7936,7 +7936,7 @@
         <v>-30</v>
       </c>
       <c r="J229">
-        <v>-78.3</v>
+        <v>-78.099999999999994</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -8096,7 +8096,7 @@
         <v>2.1</v>
       </c>
       <c r="J234">
-        <v>108.3</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -8128,7 +8128,7 @@
         <v>3.7</v>
       </c>
       <c r="J235">
-        <v>734.6</v>
+        <v>734.5</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -8160,7 +8160,7 @@
         <v>-2.1</v>
       </c>
       <c r="J236">
-        <v>-108.3</v>
+        <v>-107.9</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -8192,7 +8192,7 @@
         <v>-3.7</v>
       </c>
       <c r="J237">
-        <v>-734.6</v>
+        <v>-734.5</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -8212,7 +8212,7 @@
         <v>131.5</v>
       </c>
       <c r="F238">
-        <v>93</v>
+        <v>92.9</v>
       </c>
       <c r="G238">
         <v>3.4</v>
@@ -8224,7 +8224,7 @@
         <v>6.1</v>
       </c>
       <c r="J238">
-        <v>78.3</v>
+        <v>78.099999999999994</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -8244,7 +8244,7 @@
         <v>131.5</v>
       </c>
       <c r="F239">
-        <v>93</v>
+        <v>92.9</v>
       </c>
       <c r="G239">
         <v>3.4</v>
@@ -8276,7 +8276,7 @@
         <v>-131.5</v>
       </c>
       <c r="F240">
-        <v>-93</v>
+        <v>-92.9</v>
       </c>
       <c r="G240">
         <v>-3.4</v>
@@ -8288,7 +8288,7 @@
         <v>-6.1</v>
       </c>
       <c r="J240">
-        <v>-78.3</v>
+        <v>-78.099999999999994</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -8308,7 +8308,7 @@
         <v>-131.5</v>
       </c>
       <c r="F241">
-        <v>-93</v>
+        <v>-92.9</v>
       </c>
       <c r="G241">
         <v>-3.4</v>
@@ -8512,7 +8512,7 @@
         <v>4</v>
       </c>
       <c r="J247">
-        <v>107.4</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -8576,7 +8576,7 @@
         <v>-4</v>
       </c>
       <c r="J249">
-        <v>-107.4</v>
+        <v>-107.2</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -8640,7 +8640,7 @@
         <v>13.2</v>
       </c>
       <c r="J251">
-        <v>83.2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -8704,7 +8704,7 @@
         <v>-13.2</v>
       </c>
       <c r="J253">
-        <v>-83.2</v>
+        <v>-83</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
@@ -8832,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="J257">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
@@ -8852,7 +8852,7 @@
         <v>12</v>
       </c>
       <c r="F258">
-        <v>204.1</v>
+        <v>204</v>
       </c>
       <c r="G258">
         <v>0.9</v>
@@ -8864,7 +8864,7 @@
         <v>4</v>
       </c>
       <c r="J258">
-        <v>107.4</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
@@ -8884,7 +8884,7 @@
         <v>12</v>
       </c>
       <c r="F259">
-        <v>204.1</v>
+        <v>204</v>
       </c>
       <c r="G259">
         <v>0.9</v>
@@ -8896,7 +8896,7 @@
         <v>2.6</v>
       </c>
       <c r="J259">
-        <v>733.3</v>
+        <v>733.2</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
@@ -8916,7 +8916,7 @@
         <v>-12</v>
       </c>
       <c r="F260">
-        <v>-204.1</v>
+        <v>-204</v>
       </c>
       <c r="G260">
         <v>-0.9</v>
@@ -8928,7 +8928,7 @@
         <v>-4</v>
       </c>
       <c r="J260">
-        <v>-107.4</v>
+        <v>-107.2</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
@@ -8948,7 +8948,7 @@
         <v>-12</v>
       </c>
       <c r="F261">
-        <v>-204.1</v>
+        <v>-204</v>
       </c>
       <c r="G261">
         <v>-0.9</v>
@@ -8960,7 +8960,7 @@
         <v>-2.6</v>
       </c>
       <c r="J261">
-        <v>-733.3</v>
+        <v>-733.2</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -8980,7 +8980,7 @@
         <v>38.1</v>
       </c>
       <c r="F262">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="G262">
         <v>2.9</v>
@@ -8992,7 +8992,7 @@
         <v>13.2</v>
       </c>
       <c r="J262">
-        <v>83.2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -9012,7 +9012,7 @@
         <v>38.1</v>
       </c>
       <c r="F263">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="G263">
         <v>2.9</v>
@@ -9044,7 +9044,7 @@
         <v>-38.1</v>
       </c>
       <c r="F264">
-        <v>-93.3</v>
+        <v>-93.2</v>
       </c>
       <c r="G264">
         <v>-2.9</v>
@@ -9056,7 +9056,7 @@
         <v>-13.2</v>
       </c>
       <c r="J264">
-        <v>-83.2</v>
+        <v>-83</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -9076,7 +9076,7 @@
         <v>-38.1</v>
       </c>
       <c r="F265">
-        <v>-93.3</v>
+        <v>-93.2</v>
       </c>
       <c r="G265">
         <v>-2.9</v>
@@ -9280,7 +9280,7 @@
         <v>10.1</v>
       </c>
       <c r="J271">
-        <v>112.7</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -9344,7 +9344,7 @@
         <v>-10.1</v>
       </c>
       <c r="J273">
-        <v>-112.7</v>
+        <v>-112.5</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -9620,7 +9620,7 @@
         <v>42.8</v>
       </c>
       <c r="F282">
-        <v>201.2</v>
+        <v>201.1</v>
       </c>
       <c r="G282">
         <v>1.5</v>
@@ -9632,7 +9632,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J282">
-        <v>112.7</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.25">
@@ -9652,7 +9652,7 @@
         <v>42.8</v>
       </c>
       <c r="F283">
-        <v>201.2</v>
+        <v>201.1</v>
       </c>
       <c r="G283">
         <v>1.5</v>
@@ -9664,7 +9664,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="J283">
-        <v>729.6</v>
+        <v>729.5</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.25">
@@ -9684,7 +9684,7 @@
         <v>-42.8</v>
       </c>
       <c r="F284">
-        <v>-201.2</v>
+        <v>-201.1</v>
       </c>
       <c r="G284">
         <v>-1.5</v>
@@ -9696,7 +9696,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="J284">
-        <v>-112.7</v>
+        <v>-112.5</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
@@ -9716,7 +9716,7 @@
         <v>-42.8</v>
       </c>
       <c r="F285">
-        <v>-201.2</v>
+        <v>-201.1</v>
       </c>
       <c r="G285">
         <v>-1.5</v>
@@ -9728,7 +9728,7 @@
         <v>-4.4000000000000004</v>
       </c>
       <c r="J285">
-        <v>-729.6</v>
+        <v>-729.5</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
@@ -10007,7 +10007,7 @@
         <v>112.6</v>
       </c>
       <c r="G294">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H294">
         <v>0.7</v>
@@ -10039,16 +10039,16 @@
         <v>112.6</v>
       </c>
       <c r="G295">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H295">
         <v>0.7</v>
       </c>
       <c r="I295">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J295">
-        <v>113.4</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.25">
@@ -10071,7 +10071,7 @@
         <v>-112.6</v>
       </c>
       <c r="G296">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="H296">
         <v>-0.7</v>
@@ -10103,16 +10103,16 @@
         <v>-112.6</v>
       </c>
       <c r="G297">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="H297">
         <v>-0.7</v>
       </c>
       <c r="I297">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="J297">
-        <v>-113.4</v>
+        <v>-113.3</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.25">
@@ -10132,7 +10132,7 @@
         <v>21.9</v>
       </c>
       <c r="F298">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="G298">
         <v>2.5</v>
@@ -10144,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="J298">
-        <v>208</v>
+        <v>208.1</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.25">
@@ -10164,7 +10164,7 @@
         <v>21.9</v>
       </c>
       <c r="F299">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="G299">
         <v>2.5</v>
@@ -10196,7 +10196,7 @@
         <v>-21.9</v>
       </c>
       <c r="F300">
-        <v>-57</v>
+        <v>-57.1</v>
       </c>
       <c r="G300">
         <v>-2.5</v>
@@ -10208,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="J300">
-        <v>-208</v>
+        <v>-208.1</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
@@ -10228,7 +10228,7 @@
         <v>-21.9</v>
       </c>
       <c r="F301">
-        <v>-57</v>
+        <v>-57.1</v>
       </c>
       <c r="G301">
         <v>-2.5</v>
@@ -10397,10 +10397,10 @@
         <v>0.2</v>
       </c>
       <c r="I306">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J306">
-        <v>113.4</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
@@ -10432,7 +10432,7 @@
         <v>3.2</v>
       </c>
       <c r="J307">
-        <v>727.9</v>
+        <v>727.8</v>
       </c>
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.25">
@@ -10461,10 +10461,10 @@
         <v>-0.2</v>
       </c>
       <c r="I308">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="J308">
-        <v>-113.4</v>
+        <v>-113.3</v>
       </c>
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.25">
@@ -10496,7 +10496,7 @@
         <v>-3.2</v>
       </c>
       <c r="J309">
-        <v>-727.9</v>
+        <v>-727.8</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
@@ -10772,7 +10772,7 @@
         <v>12</v>
       </c>
       <c r="F318">
-        <v>116.3</v>
+        <v>116.4</v>
       </c>
       <c r="G318">
         <v>3.5</v>
@@ -10804,7 +10804,7 @@
         <v>12</v>
       </c>
       <c r="F319">
-        <v>116.3</v>
+        <v>116.4</v>
       </c>
       <c r="G319">
         <v>3.5</v>
@@ -10836,7 +10836,7 @@
         <v>-12</v>
       </c>
       <c r="F320">
-        <v>-116.3</v>
+        <v>-116.4</v>
       </c>
       <c r="G320">
         <v>-3.5</v>
@@ -10868,7 +10868,7 @@
         <v>-12</v>
       </c>
       <c r="F321">
-        <v>-116.3</v>
+        <v>-116.4</v>
       </c>
       <c r="G321">
         <v>-3.5</v>
@@ -10900,7 +10900,7 @@
         <v>35.9</v>
       </c>
       <c r="F322">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="G322">
         <v>10.7</v>
@@ -10912,7 +10912,7 @@
         <v>25.9</v>
       </c>
       <c r="J322">
-        <v>210.1</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
@@ -10932,7 +10932,7 @@
         <v>35.9</v>
       </c>
       <c r="F323">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="G323">
         <v>10.7</v>
@@ -10944,7 +10944,7 @@
         <v>27.5</v>
       </c>
       <c r="J323">
-        <v>139.19999999999999</v>
+        <v>139.30000000000001</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
@@ -10964,7 +10964,7 @@
         <v>-35.9</v>
       </c>
       <c r="F324">
-        <v>-61.9</v>
+        <v>-62</v>
       </c>
       <c r="G324">
         <v>-10.7</v>
@@ -10976,7 +10976,7 @@
         <v>-25.9</v>
       </c>
       <c r="J324">
-        <v>-210.1</v>
+        <v>-210.2</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
@@ -10996,7 +10996,7 @@
         <v>-35.9</v>
       </c>
       <c r="F325">
-        <v>-61.9</v>
+        <v>-62</v>
       </c>
       <c r="G325">
         <v>-10.7</v>
@@ -11008,7 +11008,7 @@
         <v>-27.5</v>
       </c>
       <c r="J325">
-        <v>-139.19999999999999</v>
+        <v>-139.30000000000001</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.25">
@@ -11200,7 +11200,7 @@
         <v>5.4</v>
       </c>
       <c r="J331">
-        <v>723.9</v>
+        <v>723.8</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
@@ -11264,7 +11264,7 @@
         <v>-5.4</v>
       </c>
       <c r="J333">
-        <v>-723.9</v>
+        <v>-723.8</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.25">
@@ -11296,7 +11296,7 @@
         <v>5</v>
       </c>
       <c r="J334">
-        <v>139.19999999999999</v>
+        <v>139.30000000000001</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.25">
@@ -11360,7 +11360,7 @@
         <v>-5</v>
       </c>
       <c r="J336">
-        <v>-139.19999999999999</v>
+        <v>-139.30000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.25">
@@ -11668,7 +11668,7 @@
         <v>17.3</v>
       </c>
       <c r="F346">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="G346">
         <v>1</v>
@@ -11680,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="J346">
-        <v>212.3</v>
+        <v>212.5</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.25">
@@ -11700,7 +11700,7 @@
         <v>17.3</v>
       </c>
       <c r="F347">
-        <v>65.7</v>
+        <v>65.8</v>
       </c>
       <c r="G347">
         <v>1</v>
@@ -11712,7 +11712,7 @@
         <v>4.8</v>
       </c>
       <c r="J347">
-        <v>153.6</v>
+        <v>153.69999999999999</v>
       </c>
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.25">
@@ -11732,7 +11732,7 @@
         <v>-17.3</v>
       </c>
       <c r="F348">
-        <v>-65.7</v>
+        <v>-65.8</v>
       </c>
       <c r="G348">
         <v>-1</v>
@@ -11744,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="J348">
-        <v>-212.3</v>
+        <v>-212.5</v>
       </c>
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.25">
@@ -11764,7 +11764,7 @@
         <v>-17.3</v>
       </c>
       <c r="F349">
-        <v>-65.7</v>
+        <v>-65.8</v>
       </c>
       <c r="G349">
         <v>-1</v>
@@ -11776,7 +11776,7 @@
         <v>-4.8</v>
       </c>
       <c r="J349">
-        <v>-153.6</v>
+        <v>-153.69999999999999</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.25">
@@ -11840,7 +11840,7 @@
         <v>0.1</v>
       </c>
       <c r="J351">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.25">
@@ -11968,7 +11968,7 @@
         <v>4.7</v>
       </c>
       <c r="J355">
-        <v>728.7</v>
+        <v>728.6</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.25">
@@ -12032,7 +12032,7 @@
         <v>-4.7</v>
       </c>
       <c r="J357">
-        <v>-728.7</v>
+        <v>-728.6</v>
       </c>
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.25">
@@ -12064,7 +12064,7 @@
         <v>4.8</v>
       </c>
       <c r="J358">
-        <v>153.6</v>
+        <v>153.69999999999999</v>
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.25">
@@ -12128,7 +12128,7 @@
         <v>-4.8</v>
       </c>
       <c r="J360">
-        <v>-153.6</v>
+        <v>-153.69999999999999</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.25">
@@ -12224,7 +12224,7 @@
         <v>2</v>
       </c>
       <c r="J363">
-        <v>-14.5</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.25">
@@ -12352,7 +12352,7 @@
         <v>3.2</v>
       </c>
       <c r="J367">
-        <v>101.3</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.25">
@@ -12416,7 +12416,7 @@
         <v>-3.2</v>
       </c>
       <c r="J369">
-        <v>-101.3</v>
+        <v>-101.2</v>
       </c>
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
@@ -12436,7 +12436,7 @@
         <v>102.8</v>
       </c>
       <c r="F370">
-        <v>36.799999999999997</v>
+        <v>36.9</v>
       </c>
       <c r="G370">
         <v>3.6</v>
@@ -12448,7 +12448,7 @@
         <v>9.1</v>
       </c>
       <c r="J370">
-        <v>138.69999999999999</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.25">
@@ -12468,7 +12468,7 @@
         <v>102.8</v>
       </c>
       <c r="F371">
-        <v>36.799999999999997</v>
+        <v>36.9</v>
       </c>
       <c r="G371">
         <v>3.6</v>
@@ -12480,7 +12480,7 @@
         <v>9.1</v>
       </c>
       <c r="J371">
-        <v>121.9</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.25">
@@ -12500,7 +12500,7 @@
         <v>-102.8</v>
       </c>
       <c r="F372">
-        <v>-36.799999999999997</v>
+        <v>-36.9</v>
       </c>
       <c r="G372">
         <v>-3.6</v>
@@ -12512,7 +12512,7 @@
         <v>-9.1</v>
       </c>
       <c r="J372">
-        <v>-138.69999999999999</v>
+        <v>-138.9</v>
       </c>
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.25">
@@ -12532,7 +12532,7 @@
         <v>-102.8</v>
       </c>
       <c r="F373">
-        <v>-36.799999999999997</v>
+        <v>-36.9</v>
       </c>
       <c r="G373">
         <v>-3.6</v>
@@ -12544,7 +12544,7 @@
         <v>-9.1</v>
       </c>
       <c r="J373">
-        <v>-121.9</v>
+        <v>-122.1</v>
       </c>
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.25">
@@ -12672,7 +12672,7 @@
         <v>0.1</v>
       </c>
       <c r="J377">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.25">
@@ -12736,7 +12736,7 @@
         <v>8</v>
       </c>
       <c r="J379">
-        <v>772.5</v>
+        <v>772.4</v>
       </c>
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
@@ -12800,7 +12800,7 @@
         <v>-8</v>
       </c>
       <c r="J381">
-        <v>-772.5</v>
+        <v>-772.4</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.25">
@@ -12817,7 +12817,7 @@
         <v>13</v>
       </c>
       <c r="E382">
-        <v>144.6</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="F382">
         <v>128.30000000000001</v>
@@ -12832,7 +12832,7 @@
         <v>14.5</v>
       </c>
       <c r="J382">
-        <v>121.7</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.25">
@@ -12849,7 +12849,7 @@
         <v>14</v>
       </c>
       <c r="E383">
-        <v>144.6</v>
+        <v>144.69999999999999</v>
       </c>
       <c r="F383">
         <v>128.30000000000001</v>
@@ -12881,7 +12881,7 @@
         <v>13</v>
       </c>
       <c r="E384">
-        <v>-144.6</v>
+        <v>-144.69999999999999</v>
       </c>
       <c r="F384">
         <v>-128.30000000000001</v>
@@ -12896,7 +12896,7 @@
         <v>-14.5</v>
       </c>
       <c r="J384">
-        <v>-121.7</v>
+        <v>-121.8</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>14</v>
       </c>
       <c r="E385">
-        <v>-144.6</v>
+        <v>-144.69999999999999</v>
       </c>
       <c r="F385">
         <v>-128.30000000000001</v>
@@ -13076,7 +13076,7 @@
         <v>130.30000000000001</v>
       </c>
       <c r="F390">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="G390">
         <v>2.2999999999999998</v>
@@ -13088,7 +13088,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="J390">
-        <v>134.19999999999999</v>
+        <v>134.1</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.25">
@@ -13108,7 +13108,7 @@
         <v>130.30000000000001</v>
       </c>
       <c r="F391">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="G391">
         <v>2.2999999999999998</v>
@@ -13120,7 +13120,7 @@
         <v>6.6</v>
       </c>
       <c r="J391">
-        <v>68.400000000000006</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.25">
@@ -13140,7 +13140,7 @@
         <v>-130.30000000000001</v>
       </c>
       <c r="F392">
-        <v>-30.8</v>
+        <v>-30.7</v>
       </c>
       <c r="G392">
         <v>-2.2999999999999998</v>
@@ -13152,7 +13152,7 @@
         <v>-5.0999999999999996</v>
       </c>
       <c r="J392">
-        <v>-134.19999999999999</v>
+        <v>-134.1</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.25">
@@ -13172,7 +13172,7 @@
         <v>-130.30000000000001</v>
       </c>
       <c r="F393">
-        <v>-30.8</v>
+        <v>-30.7</v>
       </c>
       <c r="G393">
         <v>-2.2999999999999998</v>
@@ -13184,7 +13184,7 @@
         <v>-6.6</v>
       </c>
       <c r="J393">
-        <v>-68.400000000000006</v>
+        <v>-68.2</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.25">
@@ -13204,7 +13204,7 @@
         <v>74.7</v>
       </c>
       <c r="F394">
-        <v>74.900000000000006</v>
+        <v>74.8</v>
       </c>
       <c r="G394">
         <v>1.2</v>
@@ -13236,7 +13236,7 @@
         <v>74.7</v>
       </c>
       <c r="F395">
-        <v>74.900000000000006</v>
+        <v>74.8</v>
       </c>
       <c r="G395">
         <v>1.2</v>
@@ -13268,7 +13268,7 @@
         <v>-74.7</v>
       </c>
       <c r="F396">
-        <v>-74.900000000000006</v>
+        <v>-74.8</v>
       </c>
       <c r="G396">
         <v>-1.2</v>
@@ -13300,7 +13300,7 @@
         <v>-74.7</v>
       </c>
       <c r="F397">
-        <v>-74.900000000000006</v>
+        <v>-74.8</v>
       </c>
       <c r="G397">
         <v>-1.2</v>
@@ -13460,10 +13460,10 @@
         <v>213.9</v>
       </c>
       <c r="F402">
-        <v>88.4</v>
+        <v>88.3</v>
       </c>
       <c r="G402">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H402">
         <v>0.3</v>
@@ -13472,7 +13472,7 @@
         <v>12.9</v>
       </c>
       <c r="J402">
-        <v>68.400000000000006</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.25">
@@ -13492,10 +13492,10 @@
         <v>213.9</v>
       </c>
       <c r="F403">
-        <v>88.4</v>
+        <v>88.3</v>
       </c>
       <c r="G403">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H403">
         <v>0.3</v>
@@ -13524,10 +13524,10 @@
         <v>-213.9</v>
       </c>
       <c r="F404">
-        <v>-88.4</v>
+        <v>-88.3</v>
       </c>
       <c r="G404">
-        <v>-10.1</v>
+        <v>-10</v>
       </c>
       <c r="H404">
         <v>-0.3</v>
@@ -13536,7 +13536,7 @@
         <v>-12.9</v>
       </c>
       <c r="J404">
-        <v>-68.400000000000006</v>
+        <v>-68.2</v>
       </c>
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.25">
@@ -13556,10 +13556,10 @@
         <v>-213.9</v>
       </c>
       <c r="F405">
-        <v>-88.4</v>
+        <v>-88.3</v>
       </c>
       <c r="G405">
-        <v>-10.1</v>
+        <v>-10</v>
       </c>
       <c r="H405">
         <v>-0.3</v>
@@ -13856,7 +13856,7 @@
         <v>0</v>
       </c>
       <c r="J414">
-        <v>198</v>
+        <v>197.9</v>
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.25">
@@ -13888,7 +13888,7 @@
         <v>3.2</v>
       </c>
       <c r="J415">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.25">
@@ -13920,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="J416">
-        <v>-198</v>
+        <v>-197.9</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.25">
@@ -13952,7 +13952,7 @@
         <v>-3.2</v>
       </c>
       <c r="J417">
-        <v>-105.9</v>
+        <v>-105.8</v>
       </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.25">
@@ -14016,7 +14016,7 @@
         <v>2.8</v>
       </c>
       <c r="J419">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.25">
@@ -14080,7 +14080,7 @@
         <v>-2.8</v>
       </c>
       <c r="J421">
-        <v>-102.3</v>
+        <v>-102.2</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.25">
@@ -14240,7 +14240,7 @@
         <v>3.2</v>
       </c>
       <c r="J426">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.25">
@@ -14272,7 +14272,7 @@
         <v>14.9</v>
       </c>
       <c r="J427">
-        <v>274.10000000000002</v>
+        <v>274</v>
       </c>
     </row>
     <row r="428" spans="1:10" x14ac:dyDescent="0.25">
@@ -14304,7 +14304,7 @@
         <v>-3.2</v>
       </c>
       <c r="J428">
-        <v>-105.9</v>
+        <v>-105.8</v>
       </c>
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.25">
@@ -14336,7 +14336,7 @@
         <v>-14.9</v>
       </c>
       <c r="J429">
-        <v>-274.10000000000002</v>
+        <v>-274</v>
       </c>
     </row>
     <row r="430" spans="1:10" x14ac:dyDescent="0.25">
@@ -14368,7 +14368,7 @@
         <v>2.8</v>
       </c>
       <c r="J430">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="431" spans="1:10" x14ac:dyDescent="0.25">
@@ -14432,7 +14432,7 @@
         <v>-2.8</v>
       </c>
       <c r="J432">
-        <v>-102.3</v>
+        <v>-102.2</v>
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.25">
@@ -14656,7 +14656,7 @@
         <v>17.2</v>
       </c>
       <c r="J439">
-        <v>119.8</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.25">
@@ -14720,7 +14720,7 @@
         <v>-17.2</v>
       </c>
       <c r="J441">
-        <v>-119.8</v>
+        <v>-119.7</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.25">
@@ -15008,7 +15008,7 @@
         <v>6.6</v>
       </c>
       <c r="J450">
-        <v>119.8</v>
+        <v>119.7</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.25">
@@ -15040,7 +15040,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="J451">
-        <v>276.39999999999998</v>
+        <v>276.3</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.25">
@@ -15072,7 +15072,7 @@
         <v>-6.6</v>
       </c>
       <c r="J452">
-        <v>-119.8</v>
+        <v>-119.7</v>
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.25">
@@ -15104,7 +15104,7 @@
         <v>-18.100000000000001</v>
       </c>
       <c r="J453">
-        <v>-276.39999999999998</v>
+        <v>-276.3</v>
       </c>
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.25">
@@ -15424,7 +15424,7 @@
         <v>20.8</v>
       </c>
       <c r="J463">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.25">
@@ -15488,7 +15488,7 @@
         <v>-20.8</v>
       </c>
       <c r="J465">
-        <v>-54.1</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.25">
@@ -15520,7 +15520,7 @@
         <v>5.4</v>
       </c>
       <c r="J466">
-        <v>465.7</v>
+        <v>465.6</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.25">
@@ -15584,7 +15584,7 @@
         <v>-5.4</v>
       </c>
       <c r="J468">
-        <v>-465.7</v>
+        <v>-465.6</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.25">
@@ -15773,10 +15773,10 @@
         <v>0.3</v>
       </c>
       <c r="I474">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J474">
-        <v>54.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.25">
@@ -15837,10 +15837,10 @@
         <v>-0.3</v>
       </c>
       <c r="I476">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="J476">
-        <v>-54.1</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.25">
@@ -16192,7 +16192,7 @@
         <v>11.3</v>
       </c>
       <c r="J487">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.25">
@@ -16256,7 +16256,7 @@
         <v>-11.3</v>
       </c>
       <c r="J489">
-        <v>-61.5</v>
+        <v>-61.4</v>
       </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.25">
@@ -16544,7 +16544,7 @@
         <v>11.3</v>
       </c>
       <c r="J498">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="499" spans="1:10" x14ac:dyDescent="0.25">
@@ -16608,7 +16608,7 @@
         <v>-11.3</v>
       </c>
       <c r="J500">
-        <v>-61.5</v>
+        <v>-61.4</v>
       </c>
     </row>
     <row r="501" spans="1:10" x14ac:dyDescent="0.25">
@@ -16960,7 +16960,7 @@
         <v>26.8</v>
       </c>
       <c r="J511">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.25">
@@ -17024,7 +17024,7 @@
         <v>-26.8</v>
       </c>
       <c r="J513">
-        <v>-51.6</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.25">
@@ -17088,7 +17088,7 @@
         <v>8.9</v>
       </c>
       <c r="J515">
-        <v>88.3</v>
+        <v>88.4</v>
       </c>
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.25">
@@ -17152,7 +17152,7 @@
         <v>-8.9</v>
       </c>
       <c r="J517">
-        <v>-88.3</v>
+        <v>-88.4</v>
       </c>
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.25">
@@ -17312,7 +17312,7 @@
         <v>8.6</v>
       </c>
       <c r="J522">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.25">
@@ -17376,7 +17376,7 @@
         <v>-8.6</v>
       </c>
       <c r="J524">
-        <v>-51.6</v>
+        <v>-51.5</v>
       </c>
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.25">
@@ -17440,7 +17440,7 @@
         <v>3.6</v>
       </c>
       <c r="J526">
-        <v>88.3</v>
+        <v>88.4</v>
       </c>
     </row>
     <row r="527" spans="1:10" x14ac:dyDescent="0.25">
@@ -17504,7 +17504,7 @@
         <v>-3.6</v>
       </c>
       <c r="J528">
-        <v>-88.3</v>
+        <v>-88.4</v>
       </c>
     </row>
     <row r="529" spans="1:10" x14ac:dyDescent="0.25">
@@ -17728,7 +17728,7 @@
         <v>14.4</v>
       </c>
       <c r="J535">
-        <v>32.9</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="536" spans="1:10" x14ac:dyDescent="0.25">
@@ -17792,7 +17792,7 @@
         <v>-14.4</v>
       </c>
       <c r="J537">
-        <v>-32.9</v>
+        <v>-32.799999999999997</v>
       </c>
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.25">
@@ -18080,7 +18080,7 @@
         <v>14.4</v>
       </c>
       <c r="J546">
-        <v>32.9</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="547" spans="1:10" x14ac:dyDescent="0.25">
@@ -18144,7 +18144,7 @@
         <v>-14.4</v>
       </c>
       <c r="J548">
-        <v>-32.9</v>
+        <v>-32.799999999999997</v>
       </c>
     </row>
     <row r="549" spans="1:10" x14ac:dyDescent="0.25">
@@ -18240,7 +18240,7 @@
         <v>3.7</v>
       </c>
       <c r="J551">
-        <v>811.6</v>
+        <v>811.7</v>
       </c>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.25">
@@ -18304,7 +18304,7 @@
         <v>-3.7</v>
       </c>
       <c r="J553">
-        <v>-811.6</v>
+        <v>-811.7</v>
       </c>
     </row>
     <row r="554" spans="1:10" x14ac:dyDescent="0.25">
@@ -18464,7 +18464,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="J558">
-        <v>134.6</v>
+        <v>134.69999999999999</v>
       </c>
     </row>
     <row r="559" spans="1:10" x14ac:dyDescent="0.25">
@@ -18528,7 +18528,7 @@
         <v>-16.600000000000001</v>
       </c>
       <c r="J560">
-        <v>-134.6</v>
+        <v>-134.69999999999999</v>
       </c>
     </row>
     <row r="561" spans="1:10" x14ac:dyDescent="0.25">
@@ -18833,7 +18833,7 @@
         <v>13</v>
       </c>
       <c r="E570">
-        <v>217.4</v>
+        <v>217.5</v>
       </c>
       <c r="F570">
         <v>86.6</v>
@@ -18865,7 +18865,7 @@
         <v>14</v>
       </c>
       <c r="E571">
-        <v>217.4</v>
+        <v>217.5</v>
       </c>
       <c r="F571">
         <v>86.6</v>
@@ -18897,7 +18897,7 @@
         <v>13</v>
       </c>
       <c r="E572">
-        <v>-217.4</v>
+        <v>-217.5</v>
       </c>
       <c r="F572">
         <v>-86.6</v>
@@ -18929,7 +18929,7 @@
         <v>14</v>
       </c>
       <c r="E573">
-        <v>-217.4</v>
+        <v>-217.5</v>
       </c>
       <c r="F573">
         <v>-86.6</v>
@@ -19220,7 +19220,7 @@
         <v>56.3</v>
       </c>
       <c r="F582">
-        <v>34.200000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="G582">
         <v>2.4</v>
@@ -19232,7 +19232,7 @@
         <v>0</v>
       </c>
       <c r="J582">
-        <v>149</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="583" spans="1:10" x14ac:dyDescent="0.25">
@@ -19252,7 +19252,7 @@
         <v>56.3</v>
       </c>
       <c r="F583">
-        <v>34.200000000000003</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="G583">
         <v>2.4</v>
@@ -19264,7 +19264,7 @@
         <v>11.9</v>
       </c>
       <c r="J583">
-        <v>57.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="584" spans="1:10" x14ac:dyDescent="0.25">
@@ -19284,7 +19284,7 @@
         <v>-56.3</v>
       </c>
       <c r="F584">
-        <v>-34.200000000000003</v>
+        <v>-34.299999999999997</v>
       </c>
       <c r="G584">
         <v>-2.4</v>
@@ -19296,7 +19296,7 @@
         <v>0</v>
       </c>
       <c r="J584">
-        <v>-149</v>
+        <v>-149.1</v>
       </c>
     </row>
     <row r="585" spans="1:10" x14ac:dyDescent="0.25">
@@ -19316,7 +19316,7 @@
         <v>-56.3</v>
       </c>
       <c r="F585">
-        <v>-34.200000000000003</v>
+        <v>-34.299999999999997</v>
       </c>
       <c r="G585">
         <v>-2.4</v>
@@ -19328,7 +19328,7 @@
         <v>-11.9</v>
       </c>
       <c r="J585">
-        <v>-57.9</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="586" spans="1:10" x14ac:dyDescent="0.25">
@@ -19616,7 +19616,7 @@
         <v>11.9</v>
       </c>
       <c r="J594">
-        <v>57.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="595" spans="1:10" x14ac:dyDescent="0.25">
@@ -19648,7 +19648,7 @@
         <v>11</v>
       </c>
       <c r="J595">
-        <v>275.7</v>
+        <v>275.60000000000002</v>
       </c>
     </row>
     <row r="596" spans="1:10" x14ac:dyDescent="0.25">
@@ -19680,7 +19680,7 @@
         <v>-11.9</v>
       </c>
       <c r="J596">
-        <v>-57.9</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="597" spans="1:10" x14ac:dyDescent="0.25">
@@ -19712,7 +19712,7 @@
         <v>-11</v>
       </c>
       <c r="J597">
-        <v>-275.7</v>
+        <v>-275.60000000000002</v>
       </c>
     </row>
     <row r="598" spans="1:10" x14ac:dyDescent="0.25">
@@ -19988,7 +19988,7 @@
         <v>109.7</v>
       </c>
       <c r="F606">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="G606">
         <v>7.2</v>
@@ -20000,7 +20000,7 @@
         <v>14.5</v>
       </c>
       <c r="J606">
-        <v>137.69999999999999</v>
+        <v>137.80000000000001</v>
       </c>
     </row>
     <row r="607" spans="1:10" x14ac:dyDescent="0.25">
@@ -20020,7 +20020,7 @@
         <v>109.7</v>
       </c>
       <c r="F607">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="G607">
         <v>7.2</v>
@@ -20052,7 +20052,7 @@
         <v>-109.7</v>
       </c>
       <c r="F608">
-        <v>-30.5</v>
+        <v>-30.6</v>
       </c>
       <c r="G608">
         <v>-7.2</v>
@@ -20064,7 +20064,7 @@
         <v>-14.5</v>
       </c>
       <c r="J608">
-        <v>-137.69999999999999</v>
+        <v>-137.80000000000001</v>
       </c>
     </row>
     <row r="609" spans="1:10" x14ac:dyDescent="0.25">
@@ -20084,7 +20084,7 @@
         <v>-109.7</v>
       </c>
       <c r="F609">
-        <v>-30.5</v>
+        <v>-30.6</v>
       </c>
       <c r="G609">
         <v>-7.2</v>
@@ -20128,7 +20128,7 @@
         <v>5.8</v>
       </c>
       <c r="J610">
-        <v>379.1</v>
+        <v>379</v>
       </c>
     </row>
     <row r="611" spans="1:10" x14ac:dyDescent="0.25">
@@ -20160,7 +20160,7 @@
         <v>8.5</v>
       </c>
       <c r="J611">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="612" spans="1:10" x14ac:dyDescent="0.25">
@@ -20192,7 +20192,7 @@
         <v>-5.8</v>
       </c>
       <c r="J612">
-        <v>-379.1</v>
+        <v>-379</v>
       </c>
     </row>
     <row r="613" spans="1:10" x14ac:dyDescent="0.25">
@@ -20224,7 +20224,7 @@
         <v>-8.5</v>
       </c>
       <c r="J613">
-        <v>-96.3</v>
+        <v>-96.2</v>
       </c>
     </row>
     <row r="614" spans="1:10" x14ac:dyDescent="0.25">
@@ -20288,7 +20288,7 @@
         <v>-0.6</v>
       </c>
       <c r="J615">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="616" spans="1:10" x14ac:dyDescent="0.25">
@@ -20512,7 +20512,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="J622">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="623" spans="1:10" x14ac:dyDescent="0.25">
@@ -20576,7 +20576,7 @@
         <v>-4.0999999999999996</v>
       </c>
       <c r="J624">
-        <v>-96.3</v>
+        <v>-96.2</v>
       </c>
     </row>
     <row r="625" spans="1:10" x14ac:dyDescent="0.25">
@@ -20925,7 +20925,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I635">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J635">
         <v>93.2</v>
@@ -20989,7 +20989,7 @@
         <v>-2.2999999999999998</v>
       </c>
       <c r="I637">
-        <v>-4.2</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="J637">
         <v>-93.2</v>
@@ -21056,7 +21056,7 @@
         <v>-0.2</v>
       </c>
       <c r="J639">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="640" spans="1:10" x14ac:dyDescent="0.25">
@@ -21271,13 +21271,13 @@
         <v>253.6</v>
       </c>
       <c r="G646">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H646">
         <v>0.4</v>
       </c>
       <c r="I646">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J646">
         <v>93.2</v>
@@ -21303,7 +21303,7 @@
         <v>253.6</v>
       </c>
       <c r="G647">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H647">
         <v>0.4</v>
@@ -21335,13 +21335,13 @@
         <v>-253.6</v>
       </c>
       <c r="G648">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="H648">
         <v>-0.4</v>
       </c>
       <c r="I648">
-        <v>-4.2</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="J648">
         <v>-93.2</v>
@@ -21367,7 +21367,7 @@
         <v>-253.6</v>
       </c>
       <c r="G649">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="H649">
         <v>-0.4</v>
@@ -21536,7 +21536,7 @@
         <v>9.6</v>
       </c>
       <c r="J654">
-        <v>143.4</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="655" spans="1:10" x14ac:dyDescent="0.25">
@@ -21568,7 +21568,7 @@
         <v>13.5</v>
       </c>
       <c r="J655">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="656" spans="1:10" x14ac:dyDescent="0.25">
@@ -21600,7 +21600,7 @@
         <v>-9.6</v>
       </c>
       <c r="J656">
-        <v>-143.4</v>
+        <v>-143.30000000000001</v>
       </c>
     </row>
     <row r="657" spans="1:10" x14ac:dyDescent="0.25">
@@ -21632,7 +21632,7 @@
         <v>-13.5</v>
       </c>
       <c r="J657">
-        <v>-55.9</v>
+        <v>-55.8</v>
       </c>
     </row>
     <row r="658" spans="1:10" x14ac:dyDescent="0.25">
@@ -21649,7 +21649,7 @@
         <v>13</v>
       </c>
       <c r="E658">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="F658">
         <v>72.8</v>
@@ -21681,7 +21681,7 @@
         <v>14</v>
       </c>
       <c r="E659">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="F659">
         <v>72.8</v>
@@ -21713,7 +21713,7 @@
         <v>13</v>
       </c>
       <c r="E660">
-        <v>-41.6</v>
+        <v>-41.5</v>
       </c>
       <c r="F660">
         <v>-72.8</v>
@@ -21745,7 +21745,7 @@
         <v>14</v>
       </c>
       <c r="E661">
-        <v>-41.6</v>
+        <v>-41.5</v>
       </c>
       <c r="F661">
         <v>-72.8</v>
@@ -21905,7 +21905,7 @@
         <v>13</v>
       </c>
       <c r="E666">
-        <v>155</v>
+        <v>155.1</v>
       </c>
       <c r="F666">
         <v>87.1</v>
@@ -21920,7 +21920,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="J666">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="667" spans="1:10" x14ac:dyDescent="0.25">
@@ -21937,7 +21937,7 @@
         <v>14</v>
       </c>
       <c r="E667">
-        <v>155</v>
+        <v>155.1</v>
       </c>
       <c r="F667">
         <v>87.1</v>
@@ -21969,7 +21969,7 @@
         <v>13</v>
       </c>
       <c r="E668">
-        <v>-155</v>
+        <v>-155.1</v>
       </c>
       <c r="F668">
         <v>-87.1</v>
@@ -21984,7 +21984,7 @@
         <v>-8.1999999999999993</v>
       </c>
       <c r="J668">
-        <v>-55.9</v>
+        <v>-55.8</v>
       </c>
     </row>
     <row r="669" spans="1:10" x14ac:dyDescent="0.25">
@@ -22001,7 +22001,7 @@
         <v>14</v>
       </c>
       <c r="E669">
-        <v>-155</v>
+        <v>-155.1</v>
       </c>
       <c r="F669">
         <v>-87.1</v>
@@ -22304,7 +22304,7 @@
         <v>0</v>
       </c>
       <c r="J678">
-        <v>156.69999999999999</v>
+        <v>156.6</v>
       </c>
     </row>
     <row r="679" spans="1:10" x14ac:dyDescent="0.25">
@@ -22336,7 +22336,7 @@
         <v>2.8</v>
       </c>
       <c r="J679">
-        <v>67.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="680" spans="1:10" x14ac:dyDescent="0.25">
@@ -22368,7 +22368,7 @@
         <v>0</v>
       </c>
       <c r="J680">
-        <v>-156.69999999999999</v>
+        <v>-156.6</v>
       </c>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.25">
@@ -22400,7 +22400,7 @@
         <v>-2.8</v>
       </c>
       <c r="J681">
-        <v>-67.8</v>
+        <v>-67.7</v>
       </c>
     </row>
     <row r="682" spans="1:10" x14ac:dyDescent="0.25">
@@ -22464,7 +22464,7 @@
         <v>3</v>
       </c>
       <c r="J683">
-        <v>107.2</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="684" spans="1:10" x14ac:dyDescent="0.25">
@@ -22528,7 +22528,7 @@
         <v>-3</v>
       </c>
       <c r="J685">
-        <v>-107.2</v>
+        <v>-107.1</v>
       </c>
     </row>
     <row r="686" spans="1:10" x14ac:dyDescent="0.25">
@@ -22688,7 +22688,7 @@
         <v>2.8</v>
       </c>
       <c r="J690">
-        <v>67.8</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="691" spans="1:10" x14ac:dyDescent="0.25">
@@ -22752,7 +22752,7 @@
         <v>-2.8</v>
       </c>
       <c r="J692">
-        <v>-67.8</v>
+        <v>-67.7</v>
       </c>
     </row>
     <row r="693" spans="1:10" x14ac:dyDescent="0.25">
@@ -22816,7 +22816,7 @@
         <v>3</v>
       </c>
       <c r="J694">
-        <v>107.2</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="695" spans="1:10" x14ac:dyDescent="0.25">
@@ -22880,7 +22880,7 @@
         <v>-3</v>
       </c>
       <c r="J696">
-        <v>-107.2</v>
+        <v>-107.1</v>
       </c>
     </row>
     <row r="697" spans="1:10" x14ac:dyDescent="0.25">
@@ -23104,7 +23104,7 @@
         <v>3.2</v>
       </c>
       <c r="J703" s="1">
-        <v>69.400000000000006</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="704" spans="1:10" x14ac:dyDescent="0.25">
@@ -23168,7 +23168,7 @@
         <v>-3.2</v>
       </c>
       <c r="J705" s="1">
-        <v>-69.400000000000006</v>
+        <v>-69.3</v>
       </c>
     </row>
     <row r="706" spans="1:10" x14ac:dyDescent="0.25">
@@ -23456,7 +23456,7 @@
         <v>10.7</v>
       </c>
       <c r="J714" s="1">
-        <v>78.7</v>
+        <v>78.599999999999994</v>
       </c>
     </row>
     <row r="715" spans="1:10" x14ac:dyDescent="0.25">
@@ -23520,7 +23520,7 @@
         <v>-10.7</v>
       </c>
       <c r="J716" s="1">
-        <v>-78.7</v>
+        <v>-78.599999999999994</v>
       </c>
     </row>
     <row r="717" spans="1:10" x14ac:dyDescent="0.25">
@@ -23572,7 +23572,7 @@
         <v>78.099999999999994</v>
       </c>
       <c r="F718" s="1">
-        <v>295.89999999999998</v>
+        <v>296</v>
       </c>
       <c r="G718" s="1">
         <v>6.4</v>
@@ -23584,7 +23584,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="J718" s="1">
-        <v>182</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="719" spans="1:10" x14ac:dyDescent="0.25">
@@ -23604,7 +23604,7 @@
         <v>78.099999999999994</v>
       </c>
       <c r="F719" s="1">
-        <v>295.89999999999998</v>
+        <v>296</v>
       </c>
       <c r="G719" s="1">
         <v>6.4</v>
@@ -23636,7 +23636,7 @@
         <v>-78.099999999999994</v>
       </c>
       <c r="F720" s="1">
-        <v>-295.89999999999998</v>
+        <v>-296</v>
       </c>
       <c r="G720" s="1">
         <v>-6.4</v>
@@ -23648,7 +23648,7 @@
         <v>-10.199999999999999</v>
       </c>
       <c r="J720" s="1">
-        <v>-182</v>
+        <v>-181.9</v>
       </c>
     </row>
     <row r="721" spans="1:10" x14ac:dyDescent="0.25">
@@ -23668,7 +23668,7 @@
         <v>-78.099999999999994</v>
       </c>
       <c r="F721" s="1">
-        <v>-295.89999999999998</v>
+        <v>-296</v>
       </c>
       <c r="G721" s="1">
         <v>-6.4</v>
@@ -23825,7 +23825,7 @@
         <v>13</v>
       </c>
       <c r="E726" s="1">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="F726" s="1">
         <v>30.8</v>
@@ -23840,7 +23840,7 @@
         <v>1.7</v>
       </c>
       <c r="J726" s="1">
-        <v>197.8</v>
+        <v>197.7</v>
       </c>
     </row>
     <row r="727" spans="1:10" x14ac:dyDescent="0.25">
@@ -23857,7 +23857,7 @@
         <v>14</v>
       </c>
       <c r="E727" s="1">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="F727" s="1">
         <v>30.8</v>
@@ -23872,7 +23872,7 @@
         <v>1.9</v>
       </c>
       <c r="J727" s="1">
-        <v>135.19999999999999</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="728" spans="1:10" x14ac:dyDescent="0.25">
@@ -23889,7 +23889,7 @@
         <v>13</v>
       </c>
       <c r="E728" s="1">
-        <v>-62.8</v>
+        <v>-62.9</v>
       </c>
       <c r="F728" s="1">
         <v>-30.8</v>
@@ -23904,7 +23904,7 @@
         <v>-1.7</v>
       </c>
       <c r="J728" s="1">
-        <v>-197.8</v>
+        <v>-197.7</v>
       </c>
     </row>
     <row r="729" spans="1:10" x14ac:dyDescent="0.25">
@@ -23921,7 +23921,7 @@
         <v>14</v>
       </c>
       <c r="E729" s="1">
-        <v>-62.8</v>
+        <v>-62.9</v>
       </c>
       <c r="F729" s="1">
         <v>-30.8</v>
@@ -23936,7 +23936,7 @@
         <v>-1.9</v>
       </c>
       <c r="J729" s="1">
-        <v>-135.19999999999999</v>
+        <v>-135.1</v>
       </c>
     </row>
     <row r="730" spans="1:10" x14ac:dyDescent="0.25">
@@ -24128,7 +24128,7 @@
         <v>-0.2</v>
       </c>
       <c r="J735" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="736" spans="1:10" x14ac:dyDescent="0.25">
@@ -24160,7 +24160,7 @@
         <v>0.1</v>
       </c>
       <c r="J736" s="1">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="737" spans="1:10" x14ac:dyDescent="0.25">
@@ -24224,7 +24224,7 @@
         <v>5.3</v>
       </c>
       <c r="J738" s="1">
-        <v>135.19999999999999</v>
+        <v>135.1</v>
       </c>
     </row>
     <row r="739" spans="1:10" x14ac:dyDescent="0.25">
@@ -24288,7 +24288,7 @@
         <v>-5.3</v>
       </c>
       <c r="J740" s="1">
-        <v>-135.19999999999999</v>
+        <v>-135.1</v>
       </c>
     </row>
     <row r="741" spans="1:10" x14ac:dyDescent="0.25">
@@ -25152,7 +25152,7 @@
         <v>15.1</v>
       </c>
       <c r="J767" s="1">
-        <v>408</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="768" spans="1:10" x14ac:dyDescent="0.25">
@@ -25216,7 +25216,7 @@
         <v>-15.1</v>
       </c>
       <c r="J769" s="1">
-        <v>-408</v>
+        <v>-407.9</v>
       </c>
     </row>
     <row r="770" spans="1:10" x14ac:dyDescent="0.25">
@@ -25408,7 +25408,7 @@
         <v>6</v>
       </c>
       <c r="J775" s="1">
-        <v>90.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="776" spans="1:10" x14ac:dyDescent="0.25">
@@ -25472,7 +25472,7 @@
         <v>-6</v>
       </c>
       <c r="J777" s="1">
-        <v>-90.5</v>
+        <v>-90.4</v>
       </c>
     </row>
     <row r="778" spans="1:10" x14ac:dyDescent="0.25">
@@ -25760,7 +25760,7 @@
         <v>2.5</v>
       </c>
       <c r="J786" s="1">
-        <v>90.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="787" spans="1:10" x14ac:dyDescent="0.25">
@@ -25792,7 +25792,7 @@
         <v>5.8</v>
       </c>
       <c r="J787" s="1">
-        <v>714.5</v>
+        <v>714.4</v>
       </c>
     </row>
     <row r="788" spans="1:10" x14ac:dyDescent="0.25">
@@ -25824,7 +25824,7 @@
         <v>-2.5</v>
       </c>
       <c r="J788" s="1">
-        <v>-90.5</v>
+        <v>-90.4</v>
       </c>
     </row>
     <row r="789" spans="1:10" x14ac:dyDescent="0.25">
@@ -25856,7 +25856,7 @@
         <v>-5.8</v>
       </c>
       <c r="J789" s="1">
-        <v>-714.5</v>
+        <v>-714.4</v>
       </c>
     </row>
     <row r="790" spans="1:10" x14ac:dyDescent="0.25">
@@ -26176,7 +26176,7 @@
         <v>3.5</v>
       </c>
       <c r="J799" s="1">
-        <v>90.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="800" spans="1:10" x14ac:dyDescent="0.25">
@@ -26240,7 +26240,7 @@
         <v>-3.5</v>
       </c>
       <c r="J801" s="1">
-        <v>-90.1</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="802" spans="1:10" x14ac:dyDescent="0.25">
@@ -26528,7 +26528,7 @@
         <v>3.5</v>
       </c>
       <c r="J810" s="1">
-        <v>90.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="811" spans="1:10" x14ac:dyDescent="0.25">
@@ -26592,7 +26592,7 @@
         <v>-3.5</v>
       </c>
       <c r="J812" s="1">
-        <v>-90.1</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="813" spans="1:10" x14ac:dyDescent="0.25">
@@ -26644,7 +26644,7 @@
         <v>64.3</v>
       </c>
       <c r="F814" s="1">
-        <v>132.1</v>
+        <v>132</v>
       </c>
       <c r="G814" s="1">
         <v>2.4</v>
@@ -26676,7 +26676,7 @@
         <v>64.3</v>
       </c>
       <c r="F815" s="1">
-        <v>132.1</v>
+        <v>132</v>
       </c>
       <c r="G815" s="1">
         <v>2.4</v>
@@ -26708,7 +26708,7 @@
         <v>-64.3</v>
       </c>
       <c r="F816" s="1">
-        <v>-132.1</v>
+        <v>-132</v>
       </c>
       <c r="G816" s="1">
         <v>-2.4</v>
@@ -26740,7 +26740,7 @@
         <v>-64.3</v>
       </c>
       <c r="F817" s="1">
-        <v>-132.1</v>
+        <v>-132</v>
       </c>
       <c r="G817" s="1">
         <v>-2.4</v>
@@ -27028,7 +27028,7 @@
         <v>185.1</v>
       </c>
       <c r="F826" s="1">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="G826" s="1">
         <v>7.9</v>
@@ -27040,7 +27040,7 @@
         <v>15.5</v>
       </c>
       <c r="J826" s="1">
-        <v>209</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="827" spans="1:10" x14ac:dyDescent="0.25">
@@ -27060,7 +27060,7 @@
         <v>185.1</v>
       </c>
       <c r="F827" s="1">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="G827" s="1">
         <v>7.9</v>
@@ -27092,7 +27092,7 @@
         <v>-185.1</v>
       </c>
       <c r="F828" s="1">
-        <v>-53.6</v>
+        <v>-53.5</v>
       </c>
       <c r="G828" s="1">
         <v>-7.9</v>
@@ -27104,7 +27104,7 @@
         <v>-15.5</v>
       </c>
       <c r="J828" s="1">
-        <v>-209</v>
+        <v>-208.9</v>
       </c>
     </row>
     <row r="829" spans="1:10" x14ac:dyDescent="0.25">
@@ -27124,7 +27124,7 @@
         <v>-185.1</v>
       </c>
       <c r="F829" s="1">
-        <v>-53.6</v>
+        <v>-53.5</v>
       </c>
       <c r="G829" s="1">
         <v>-7.9</v>
@@ -27328,7 +27328,7 @@
         <v>4.5</v>
       </c>
       <c r="J835" s="1">
-        <v>716.5</v>
+        <v>716.4</v>
       </c>
     </row>
     <row r="836" spans="1:10" x14ac:dyDescent="0.25">
@@ -27392,7 +27392,7 @@
         <v>-4.5</v>
       </c>
       <c r="J837" s="1">
-        <v>-716.5</v>
+        <v>-716.4</v>
       </c>
     </row>
     <row r="838" spans="1:10" x14ac:dyDescent="0.25">
@@ -27808,7 +27808,7 @@
         <v>0</v>
       </c>
       <c r="J850" s="1">
-        <v>239.5</v>
+        <v>239.4</v>
       </c>
     </row>
     <row r="851" spans="1:10" x14ac:dyDescent="0.25">
@@ -27872,7 +27872,7 @@
         <v>0</v>
       </c>
       <c r="J852" s="1">
-        <v>-239.5</v>
+        <v>-239.4</v>
       </c>
     </row>
     <row r="853" spans="1:10" x14ac:dyDescent="0.25">
@@ -28096,7 +28096,7 @@
         <v>2.9</v>
       </c>
       <c r="J859" s="1">
-        <v>716.2</v>
+        <v>716.1</v>
       </c>
     </row>
     <row r="860" spans="1:10" x14ac:dyDescent="0.25">
@@ -28160,7 +28160,7 @@
         <v>-2.9</v>
       </c>
       <c r="J861" s="1">
-        <v>-716.2</v>
+        <v>-716.1</v>
       </c>
     </row>
     <row r="862" spans="1:10" x14ac:dyDescent="0.25">
@@ -28436,7 +28436,7 @@
         <v>45.7</v>
       </c>
       <c r="F870" s="1">
-        <v>68.2</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="G870" s="1">
         <v>1.9</v>
@@ -28468,7 +28468,7 @@
         <v>45.7</v>
       </c>
       <c r="F871" s="1">
-        <v>68.2</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="G871" s="1">
         <v>1.9</v>
@@ -28500,7 +28500,7 @@
         <v>-45.7</v>
       </c>
       <c r="F872" s="1">
-        <v>-68.2</v>
+        <v>-68.099999999999994</v>
       </c>
       <c r="G872" s="1">
         <v>-1.9</v>
@@ -28532,7 +28532,7 @@
         <v>-45.7</v>
       </c>
       <c r="F873" s="1">
-        <v>-68.2</v>
+        <v>-68.099999999999994</v>
       </c>
       <c r="G873" s="1">
         <v>-1.9</v>
@@ -28608,7 +28608,7 @@
         <v>19</v>
       </c>
       <c r="J875" s="1">
-        <v>108.8</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="876" spans="1:10" x14ac:dyDescent="0.25">
@@ -28672,7 +28672,7 @@
         <v>-19</v>
       </c>
       <c r="J877" s="1">
-        <v>-108.8</v>
+        <v>-108.7</v>
       </c>
     </row>
     <row r="878" spans="1:10" x14ac:dyDescent="0.25">
@@ -28960,7 +28960,7 @@
         <v>4.2</v>
       </c>
       <c r="J886" s="1">
-        <v>108.8</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="887" spans="1:10" x14ac:dyDescent="0.25">
@@ -29024,7 +29024,7 @@
         <v>-4.2</v>
       </c>
       <c r="J888" s="1">
-        <v>-108.8</v>
+        <v>-108.7</v>
       </c>
     </row>
     <row r="889" spans="1:10" x14ac:dyDescent="0.25">
@@ -29248,7 +29248,7 @@
         <v>1.7</v>
       </c>
       <c r="J895" s="1">
-        <v>98.4</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="896" spans="1:10" x14ac:dyDescent="0.25">
@@ -29312,7 +29312,7 @@
         <v>-1.7</v>
       </c>
       <c r="J897" s="1">
-        <v>-98.4</v>
+        <v>-98.3</v>
       </c>
     </row>
     <row r="898" spans="1:10" x14ac:dyDescent="0.25">
@@ -29344,7 +29344,7 @@
         <v>0</v>
       </c>
       <c r="J898" s="1">
-        <v>288.7</v>
+        <v>288.60000000000002</v>
       </c>
     </row>
     <row r="899" spans="1:10" x14ac:dyDescent="0.25">
@@ -29376,7 +29376,7 @@
         <v>5.5</v>
       </c>
       <c r="J899" s="1">
-        <v>120.4</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="900" spans="1:10" x14ac:dyDescent="0.25">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="J900" s="1">
-        <v>-288.7</v>
+        <v>-288.60000000000002</v>
       </c>
     </row>
     <row r="901" spans="1:10" x14ac:dyDescent="0.25">
@@ -29440,7 +29440,7 @@
         <v>-5.5</v>
       </c>
       <c r="J901" s="1">
-        <v>-120.4</v>
+        <v>-120.3</v>
       </c>
     </row>
     <row r="902" spans="1:10" x14ac:dyDescent="0.25">
@@ -29600,7 +29600,7 @@
         <v>1.7</v>
       </c>
       <c r="J906" s="1">
-        <v>98.4</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="907" spans="1:10" x14ac:dyDescent="0.25">
@@ -29632,7 +29632,7 @@
         <v>2.9</v>
       </c>
       <c r="J907" s="1">
-        <v>714.2</v>
+        <v>714.1</v>
       </c>
     </row>
     <row r="908" spans="1:10" x14ac:dyDescent="0.25">
@@ -29664,7 +29664,7 @@
         <v>-1.7</v>
       </c>
       <c r="J908" s="1">
-        <v>-98.4</v>
+        <v>-98.3</v>
       </c>
     </row>
     <row r="909" spans="1:10" x14ac:dyDescent="0.25">
@@ -29696,7 +29696,7 @@
         <v>-2.9</v>
       </c>
       <c r="J909" s="1">
-        <v>-714.2</v>
+        <v>-714.1</v>
       </c>
     </row>
     <row r="910" spans="1:10" x14ac:dyDescent="0.25">
@@ -29716,7 +29716,7 @@
         <v>47.2</v>
       </c>
       <c r="F910" s="1">
-        <v>98.5</v>
+        <v>98.4</v>
       </c>
       <c r="G910" s="1">
         <v>1.6</v>
@@ -29728,7 +29728,7 @@
         <v>5.5</v>
       </c>
       <c r="J910" s="1">
-        <v>120.4</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="911" spans="1:10" x14ac:dyDescent="0.25">
@@ -29748,7 +29748,7 @@
         <v>47.2</v>
       </c>
       <c r="F911" s="1">
-        <v>98.5</v>
+        <v>98.4</v>
       </c>
       <c r="G911" s="1">
         <v>1.6</v>
@@ -29780,7 +29780,7 @@
         <v>-47.2</v>
       </c>
       <c r="F912" s="1">
-        <v>-98.5</v>
+        <v>-98.4</v>
       </c>
       <c r="G912" s="1">
         <v>-1.6</v>
@@ -29792,7 +29792,7 @@
         <v>-5.5</v>
       </c>
       <c r="J912" s="1">
-        <v>-120.4</v>
+        <v>-120.3</v>
       </c>
     </row>
     <row r="913" spans="1:10" x14ac:dyDescent="0.25">
@@ -29812,7 +29812,7 @@
         <v>-47.2</v>
       </c>
       <c r="F913" s="1">
-        <v>-98.5</v>
+        <v>-98.4</v>
       </c>
       <c r="G913" s="1">
         <v>-1.6</v>
@@ -30752,7 +30752,7 @@
         <v>1.8</v>
       </c>
       <c r="J942">
-        <v>196.9</v>
+        <v>197</v>
       </c>
     </row>
     <row r="943" spans="1:10" x14ac:dyDescent="0.25">
@@ -30784,7 +30784,7 @@
         <v>2.1</v>
       </c>
       <c r="J943">
-        <v>127.3</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="944" spans="1:10" x14ac:dyDescent="0.25">
@@ -30816,7 +30816,7 @@
         <v>-1.8</v>
       </c>
       <c r="J944">
-        <v>-196.9</v>
+        <v>-197</v>
       </c>
     </row>
     <row r="945" spans="1:10" x14ac:dyDescent="0.25">
@@ -30848,7 +30848,7 @@
         <v>-2.1</v>
       </c>
       <c r="J945">
-        <v>-127.3</v>
+        <v>-127.5</v>
       </c>
     </row>
     <row r="946" spans="1:10" x14ac:dyDescent="0.25">
@@ -31124,7 +31124,7 @@
         <v>143.9</v>
       </c>
       <c r="F954">
-        <v>37.1</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G954">
         <v>8.6999999999999993</v>
@@ -31136,7 +31136,7 @@
         <v>10.5</v>
       </c>
       <c r="J954">
-        <v>127.4</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="955" spans="1:10" x14ac:dyDescent="0.25">
@@ -31156,7 +31156,7 @@
         <v>143.9</v>
       </c>
       <c r="F955">
-        <v>37.1</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="G955">
         <v>8.6999999999999993</v>
@@ -31188,7 +31188,7 @@
         <v>-143.9</v>
       </c>
       <c r="F956">
-        <v>-37.1</v>
+        <v>-37.200000000000003</v>
       </c>
       <c r="G956">
         <v>-8.6999999999999993</v>
@@ -31200,7 +31200,7 @@
         <v>-10.5</v>
       </c>
       <c r="J956">
-        <v>-127.4</v>
+        <v>-127.5</v>
       </c>
     </row>
     <row r="957" spans="1:10" x14ac:dyDescent="0.25">
@@ -31220,7 +31220,7 @@
         <v>-143.9</v>
       </c>
       <c r="F957">
-        <v>-37.1</v>
+        <v>-37.200000000000003</v>
       </c>
       <c r="G957">
         <v>-8.6999999999999993</v>
@@ -31508,7 +31508,7 @@
         <v>54.3</v>
       </c>
       <c r="F966">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G966">
         <v>0.6</v>
@@ -31520,7 +31520,7 @@
         <v>0</v>
       </c>
       <c r="J966">
-        <v>235.9</v>
+        <v>236</v>
       </c>
     </row>
     <row r="967" spans="1:10" x14ac:dyDescent="0.25">
@@ -31540,7 +31540,7 @@
         <v>54.3</v>
       </c>
       <c r="F967">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="G967">
         <v>0.6</v>
@@ -31552,7 +31552,7 @@
         <v>2.9</v>
       </c>
       <c r="J967">
-        <v>144.6</v>
+        <v>144.69999999999999</v>
       </c>
     </row>
     <row r="968" spans="1:10" x14ac:dyDescent="0.25">
@@ -31572,7 +31572,7 @@
         <v>-54.3</v>
       </c>
       <c r="F968">
-        <v>-75.2</v>
+        <v>-75.3</v>
       </c>
       <c r="G968">
         <v>-0.6</v>
@@ -31584,7 +31584,7 @@
         <v>0</v>
       </c>
       <c r="J968">
-        <v>-235.9</v>
+        <v>-236</v>
       </c>
     </row>
     <row r="969" spans="1:10" x14ac:dyDescent="0.25">
@@ -31604,7 +31604,7 @@
         <v>-54.3</v>
       </c>
       <c r="F969">
-        <v>-75.2</v>
+        <v>-75.3</v>
       </c>
       <c r="G969">
         <v>-0.6</v>
@@ -31616,7 +31616,7 @@
         <v>-2.9</v>
       </c>
       <c r="J969">
-        <v>-144.6</v>
+        <v>-144.69999999999999</v>
       </c>
     </row>
     <row r="970" spans="1:10" x14ac:dyDescent="0.25">
@@ -31680,7 +31680,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J971">
-        <v>454.7</v>
+        <v>454.6</v>
       </c>
     </row>
     <row r="972" spans="1:10" x14ac:dyDescent="0.25">
@@ -31744,7 +31744,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="J973">
-        <v>-454.7</v>
+        <v>-454.6</v>
       </c>
     </row>
     <row r="974" spans="1:10" x14ac:dyDescent="0.25">
@@ -31892,7 +31892,7 @@
         <v>54.3</v>
       </c>
       <c r="F978">
-        <v>37.700000000000003</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="G978">
         <v>5.4</v>
@@ -31904,7 +31904,7 @@
         <v>2.9</v>
       </c>
       <c r="J978">
-        <v>144.6</v>
+        <v>144.69999999999999</v>
       </c>
     </row>
     <row r="979" spans="1:10" x14ac:dyDescent="0.25">
@@ -31924,7 +31924,7 @@
         <v>54.3</v>
       </c>
       <c r="F979">
-        <v>37.700000000000003</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="G979">
         <v>5.4</v>
@@ -31956,7 +31956,7 @@
         <v>-54.3</v>
       </c>
       <c r="F980">
-        <v>-37.700000000000003</v>
+        <v>-37.799999999999997</v>
       </c>
       <c r="G980">
         <v>-5.4</v>
@@ -31968,7 +31968,7 @@
         <v>-2.9</v>
       </c>
       <c r="J980">
-        <v>-144.6</v>
+        <v>-144.69999999999999</v>
       </c>
     </row>
     <row r="981" spans="1:10" x14ac:dyDescent="0.25">
@@ -31988,7 +31988,7 @@
         <v>-54.3</v>
       </c>
       <c r="F981">
-        <v>-37.700000000000003</v>
+        <v>-37.799999999999997</v>
       </c>
       <c r="G981">
         <v>-5.4</v>
@@ -32032,7 +32032,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J982">
-        <v>454.7</v>
+        <v>454.6</v>
       </c>
     </row>
     <row r="983" spans="1:10" x14ac:dyDescent="0.25">
@@ -32096,7 +32096,7 @@
         <v>-2.2000000000000002</v>
       </c>
       <c r="J984">
-        <v>-454.7</v>
+        <v>-454.6</v>
       </c>
     </row>
     <row r="985" spans="1:10" x14ac:dyDescent="0.25">
@@ -32276,7 +32276,7 @@
         <v>72</v>
       </c>
       <c r="F990">
-        <v>72.3</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="G990">
         <v>0.7</v>
@@ -32308,7 +32308,7 @@
         <v>72</v>
       </c>
       <c r="F991">
-        <v>72.3</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="G991">
         <v>0.7</v>
@@ -32320,7 +32320,7 @@
         <v>2</v>
       </c>
       <c r="J991">
-        <v>97.7</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="992" spans="1:10" x14ac:dyDescent="0.25">
@@ -32340,7 +32340,7 @@
         <v>-72</v>
       </c>
       <c r="F992">
-        <v>-72.3</v>
+        <v>-72.400000000000006</v>
       </c>
       <c r="G992">
         <v>-0.7</v>
@@ -32372,7 +32372,7 @@
         <v>-72</v>
       </c>
       <c r="F993">
-        <v>-72.3</v>
+        <v>-72.400000000000006</v>
       </c>
       <c r="G993">
         <v>-0.7</v>
@@ -32384,7 +32384,7 @@
         <v>-2</v>
       </c>
       <c r="J993">
-        <v>-97.7</v>
+        <v>-97.9</v>
       </c>
     </row>
     <row r="994" spans="1:10" x14ac:dyDescent="0.25">
@@ -32672,7 +32672,7 @@
         <v>2</v>
       </c>
       <c r="J1002">
-        <v>97.7</v>
+        <v>97.9</v>
       </c>
     </row>
     <row r="1003" spans="1:10" x14ac:dyDescent="0.25">
@@ -32736,7 +32736,7 @@
         <v>-2</v>
       </c>
       <c r="J1004">
-        <v>-97.7</v>
+        <v>-97.9</v>
       </c>
     </row>
     <row r="1005" spans="1:10" x14ac:dyDescent="0.25">
@@ -32788,7 +32788,7 @@
         <v>124.6</v>
       </c>
       <c r="F1006">
-        <v>113.9</v>
+        <v>113.8</v>
       </c>
       <c r="G1006">
         <v>1.4</v>
@@ -32820,7 +32820,7 @@
         <v>124.6</v>
       </c>
       <c r="F1007">
-        <v>113.9</v>
+        <v>113.8</v>
       </c>
       <c r="G1007">
         <v>1.4</v>
@@ -32852,7 +32852,7 @@
         <v>-124.6</v>
       </c>
       <c r="F1008">
-        <v>-113.9</v>
+        <v>-113.8</v>
       </c>
       <c r="G1008">
         <v>-1.4</v>
@@ -32884,7 +32884,7 @@
         <v>-124.6</v>
       </c>
       <c r="F1009">
-        <v>-113.9</v>
+        <v>-113.8</v>
       </c>
       <c r="G1009">
         <v>-1.4</v>
@@ -33044,7 +33044,7 @@
         <v>35.1</v>
       </c>
       <c r="F1014">
-        <v>129.1</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="G1014">
         <v>1.8</v>
@@ -33076,7 +33076,7 @@
         <v>35.1</v>
       </c>
       <c r="F1015">
-        <v>129.1</v>
+        <v>129.19999999999999</v>
       </c>
       <c r="G1015">
         <v>1.8</v>
@@ -33088,7 +33088,7 @@
         <v>5.8</v>
       </c>
       <c r="J1015">
-        <v>151.80000000000001</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1016" spans="1:10" x14ac:dyDescent="0.25">
@@ -33108,7 +33108,7 @@
         <v>-35.1</v>
       </c>
       <c r="F1016">
-        <v>-129.1</v>
+        <v>-129.19999999999999</v>
       </c>
       <c r="G1016">
         <v>-1.8</v>
@@ -33140,7 +33140,7 @@
         <v>-35.1</v>
       </c>
       <c r="F1017">
-        <v>-129.1</v>
+        <v>-129.19999999999999</v>
       </c>
       <c r="G1017">
         <v>-1.8</v>
@@ -33152,7 +33152,7 @@
         <v>-5.8</v>
       </c>
       <c r="J1017">
-        <v>-151.80000000000001</v>
+        <v>-152</v>
       </c>
     </row>
     <row r="1018" spans="1:10" x14ac:dyDescent="0.25">
@@ -33216,7 +33216,7 @@
         <v>17.2</v>
       </c>
       <c r="J1019">
-        <v>99.1</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="1020" spans="1:10" x14ac:dyDescent="0.25">
@@ -33280,7 +33280,7 @@
         <v>-17.2</v>
       </c>
       <c r="J1021">
-        <v>-99.1</v>
+        <v>-99.2</v>
       </c>
     </row>
     <row r="1022" spans="1:10" x14ac:dyDescent="0.25">
@@ -33440,7 +33440,7 @@
         <v>6.8</v>
       </c>
       <c r="J1026">
-        <v>120.2</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="1027" spans="1:10" x14ac:dyDescent="0.25">
@@ -33504,7 +33504,7 @@
         <v>-6.8</v>
       </c>
       <c r="J1028">
-        <v>-120.2</v>
+        <v>-120.3</v>
       </c>
     </row>
     <row r="1029" spans="1:10" x14ac:dyDescent="0.25">
@@ -33824,7 +33824,7 @@
         <v>0</v>
       </c>
       <c r="J1038">
-        <v>561.6</v>
+        <v>561.70000000000005</v>
       </c>
     </row>
     <row r="1039" spans="1:10" x14ac:dyDescent="0.25">
@@ -33856,7 +33856,7 @@
         <v>4.3</v>
       </c>
       <c r="J1039">
-        <v>142.30000000000001</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="1040" spans="1:10" x14ac:dyDescent="0.25">
@@ -33888,7 +33888,7 @@
         <v>0</v>
       </c>
       <c r="J1040">
-        <v>-561.6</v>
+        <v>-561.70000000000005</v>
       </c>
     </row>
     <row r="1041" spans="1:10" x14ac:dyDescent="0.25">
@@ -33920,7 +33920,7 @@
         <v>-4.3</v>
       </c>
       <c r="J1041">
-        <v>-142.30000000000001</v>
+        <v>-142.4</v>
       </c>
     </row>
     <row r="1042" spans="1:10" x14ac:dyDescent="0.25">
@@ -33940,7 +33940,7 @@
         <v>61.3</v>
       </c>
       <c r="F1042">
-        <v>80.099999999999994</v>
+        <v>80.2</v>
       </c>
       <c r="G1042">
         <v>2.4</v>
@@ -33972,7 +33972,7 @@
         <v>61.3</v>
       </c>
       <c r="F1043">
-        <v>80.099999999999994</v>
+        <v>80.2</v>
       </c>
       <c r="G1043">
         <v>2.4</v>
@@ -34004,7 +34004,7 @@
         <v>-61.3</v>
       </c>
       <c r="F1044">
-        <v>-80.099999999999994</v>
+        <v>-80.2</v>
       </c>
       <c r="G1044">
         <v>-2.4</v>
@@ -34036,7 +34036,7 @@
         <v>-61.3</v>
       </c>
       <c r="F1045">
-        <v>-80.099999999999994</v>
+        <v>-80.2</v>
       </c>
       <c r="G1045">
         <v>-2.4</v>
@@ -34208,7 +34208,7 @@
         <v>4.3</v>
       </c>
       <c r="J1050">
-        <v>142.30000000000001</v>
+        <v>142.4</v>
       </c>
     </row>
     <row r="1051" spans="1:10" x14ac:dyDescent="0.25">
@@ -34272,7 +34272,7 @@
         <v>-4.3</v>
       </c>
       <c r="J1052">
-        <v>-142.30000000000001</v>
+        <v>-142.4</v>
       </c>
     </row>
     <row r="1053" spans="1:10" x14ac:dyDescent="0.25">
@@ -34368,7 +34368,7 @@
         <v>4.7</v>
       </c>
       <c r="J1055">
-        <v>268.39999999999998</v>
+        <v>268.3</v>
       </c>
     </row>
     <row r="1056" spans="1:10" x14ac:dyDescent="0.25">
@@ -34432,7 +34432,7 @@
         <v>-4.7</v>
       </c>
       <c r="J1057">
-        <v>-268.39999999999998</v>
+        <v>-268.3</v>
       </c>
     </row>
     <row r="1058" spans="1:10" x14ac:dyDescent="0.25">
@@ -34624,7 +34624,7 @@
         <v>3.2</v>
       </c>
       <c r="J1063">
-        <v>169</v>
+        <v>169.1</v>
       </c>
     </row>
     <row r="1064" spans="1:10" x14ac:dyDescent="0.25">
@@ -34688,7 +34688,7 @@
         <v>-3.2</v>
       </c>
       <c r="J1065">
-        <v>-169</v>
+        <v>-169.1</v>
       </c>
     </row>
     <row r="1066" spans="1:10" x14ac:dyDescent="0.25">
@@ -34976,7 +34976,7 @@
         <v>4.5</v>
       </c>
       <c r="J1074">
-        <v>146.1</v>
+        <v>146.19999999999999</v>
       </c>
     </row>
     <row r="1075" spans="1:10" x14ac:dyDescent="0.25">
@@ -35040,7 +35040,7 @@
         <v>-4.5</v>
       </c>
       <c r="J1076">
-        <v>-146.1</v>
+        <v>-146.19999999999999</v>
       </c>
     </row>
     <row r="1077" spans="1:10" x14ac:dyDescent="0.25">
@@ -35089,7 +35089,7 @@
         <v>13</v>
       </c>
       <c r="E1078">
-        <v>456.6</v>
+        <v>456.7</v>
       </c>
       <c r="F1078">
         <v>93.6</v>
@@ -35104,7 +35104,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="J1078">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="1079" spans="1:10" x14ac:dyDescent="0.25">
@@ -35121,7 +35121,7 @@
         <v>14</v>
       </c>
       <c r="E1079">
-        <v>456.6</v>
+        <v>456.7</v>
       </c>
       <c r="F1079">
         <v>93.6</v>
@@ -35136,7 +35136,7 @@
         <v>4.8</v>
       </c>
       <c r="J1079">
-        <v>304.89999999999998</v>
+        <v>304.8</v>
       </c>
     </row>
     <row r="1080" spans="1:10" x14ac:dyDescent="0.25">
@@ -35153,7 +35153,7 @@
         <v>13</v>
       </c>
       <c r="E1080">
-        <v>-456.6</v>
+        <v>-456.7</v>
       </c>
       <c r="F1080">
         <v>-93.6</v>
@@ -35168,7 +35168,7 @@
         <v>-10.199999999999999</v>
       </c>
       <c r="J1080">
-        <v>-107.6</v>
+        <v>-107.5</v>
       </c>
     </row>
     <row r="1081" spans="1:10" x14ac:dyDescent="0.25">
@@ -35185,7 +35185,7 @@
         <v>14</v>
       </c>
       <c r="E1081">
-        <v>-456.6</v>
+        <v>-456.7</v>
       </c>
       <c r="F1081">
         <v>-93.6</v>
@@ -35200,7 +35200,7 @@
         <v>-4.8</v>
       </c>
       <c r="J1081">
-        <v>-304.89999999999998</v>
+        <v>-304.8</v>
       </c>
     </row>
   </sheetData>
